--- a/elastic_search/habr_serp_data.xlsx
+++ b/elastic_search/habr_serp_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="529">
   <si>
     <t>relevance</t>
   </si>
@@ -39,6 +39,12 @@
     <t>score</t>
   </si>
   <si>
+    <t>ml_score</t>
+  </si>
+  <si>
+    <t>combined_score</t>
+  </si>
+  <si>
     <t>title</t>
   </si>
   <si>
@@ -81,6 +87,51 @@
     <t>Теги:MLмасштабированиеdockerkubernetesaiархитектура по, ML, масштабирование, docker, kubernetes, ai, архитектура по</t>
   </si>
   <si>
+    <t>ML-эксперименты проще с ClearML</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/901072/</t>
+  </si>
+  <si>
+    <t>kochetkover</t>
+  </si>
+  <si>
+    <t>2025-04-15T13:01:29.000Z</t>
+  </si>
+  <si>
+    <t>Машинное обучение * Искусственный интеллект, Машинное обучение * Искусственный интеллект, Машинное обучение *, Машинное обучение *, *, Искусственный интеллект, Искусственный интеллект, Машинное обучение, Искусственный интеллект</t>
+  </si>
+  <si>
+    <t>Теги:clearmlmachinelearningmachine-learningaiartificial intelligence, clearml, machinelearning, machine-learning, ai, artificial intelligence</t>
+  </si>
+  <si>
+    <t>Запуск ML-экспериментов через ClearML</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902148/</t>
+  </si>
+  <si>
+    <t>2025-04-18T12:26:59.000Z</t>
+  </si>
+  <si>
+    <t>Теги:clearmlmachinelearningmachine-learningartificial intelligenceartificial neural network, clearml, machinelearning, machine-learning, artificial intelligence, artificial neural network</t>
+  </si>
+  <si>
+    <t>Организация ML-проекта с примерами</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/900788/</t>
+  </si>
+  <si>
+    <t>2025-04-14T16:00:24.000Z</t>
+  </si>
+  <si>
+    <t>Машинное обучение * Искусственный интеллектPython *, Машинное обучение * Искусственный интеллектPython *, Машинное обучение *, Машинное обучение *, *, Искусственный интеллект, Искусственный интеллект, Python *, Python *, *, Машинное обучение, Искусственный интеллект, Python</t>
+  </si>
+  <si>
+    <t>Теги:машинное+обучениеискусственный интеллект, машинное+обучение, искусственный интеллект</t>
+  </si>
+  <si>
     <t>Есть ли у AMD перспективы в AI/ML/DL. Часть 1</t>
   </si>
   <si>
@@ -117,6 +168,24 @@
     <t>Теги:cybersecurityaimlкибербезопасностьдипфейки, cybersecurity, ai, ml, кибербезопасность, дипфейки</t>
   </si>
   <si>
+    <t>Cast AI привлекает $108 млн для максимальной отдачи от AI</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/906074/</t>
+  </si>
+  <si>
+    <t>dilnaz_04</t>
+  </si>
+  <si>
+    <t>2025-04-30T16:41:09.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании BotHubИскусственный интеллект, Блог компании BotHubИскусственный интеллект, Блог компании BotHub, Блог компании BotHub, Искусственный интеллект, Искусственный интеллект, Блог компании BotHub, Искусственный интеллект</t>
+  </si>
+  <si>
+    <t>Теги:AIcast aiфинансирование, AI, cast ai, финансирование</t>
+  </si>
+  <si>
     <t>Как тарифицировать AI-функционал</t>
   </si>
   <si>
@@ -135,67 +204,22 @@
     <t>Теги:saasискусственный интеллектбизнес-модельподпискимонетизациястратегияAI-ценообразование, saas, искусственный интеллект, бизнес-модель, подписки, монетизация, стратегия, AI-ценообразование</t>
   </si>
   <si>
-    <t>Cast AI привлекает $108 млн для максимальной отдачи от AI</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/906074/</t>
-  </si>
-  <si>
-    <t>dilnaz_04</t>
-  </si>
-  <si>
-    <t>2025-04-30T16:41:09.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании BotHubИскусственный интеллект, Блог компании BotHubИскусственный интеллект, Блог компании BotHub, Блог компании BotHub, Искусственный интеллект, Искусственный интеллект, Блог компании BotHub, Искусственный интеллект</t>
-  </si>
-  <si>
-    <t>Теги:AIcast aiфинансирование, AI, cast ai, финансирование</t>
-  </si>
-  <si>
-    <t>ML-эксперименты проще с ClearML</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/901072/</t>
-  </si>
-  <si>
-    <t>kochetkover</t>
-  </si>
-  <si>
-    <t>2025-04-15T13:01:29.000Z</t>
-  </si>
-  <si>
-    <t>Машинное обучение * Искусственный интеллект, Машинное обучение * Искусственный интеллект, Машинное обучение *, Машинное обучение *, *, Искусственный интеллект, Искусственный интеллект, Машинное обучение, Искусственный интеллект</t>
-  </si>
-  <si>
-    <t>Теги:clearmlmachinelearningmachine-learningaiartificial intelligence, clearml, machinelearning, machine-learning, ai, artificial intelligence</t>
-  </si>
-  <si>
-    <t>Организация ML-проекта с примерами</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/900788/</t>
-  </si>
-  <si>
-    <t>2025-04-14T16:00:24.000Z</t>
-  </si>
-  <si>
-    <t>Машинное обучение * Искусственный интеллектPython *, Машинное обучение * Искусственный интеллектPython *, Машинное обучение *, Машинное обучение *, *, Искусственный интеллект, Искусственный интеллект, Python *, Python *, *, Машинное обучение, Искусственный интеллект, Python</t>
-  </si>
-  <si>
-    <t>Теги:машинное+обучениеискусственный интеллект, машинное+обучение, искусственный интеллект</t>
-  </si>
-  <si>
-    <t>Запуск ML-экспериментов через ClearML</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902148/</t>
-  </si>
-  <si>
-    <t>2025-04-18T12:26:59.000Z</t>
-  </si>
-  <si>
-    <t>Теги:clearmlmachinelearningmachine-learningartificial intelligenceartificial neural network, clearml, machinelearning, machine-learning, artificial intelligence, artificial neural network</t>
+    <t>Как тестировать AI-агентов, чтобы не было больно</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902598/</t>
+  </si>
+  <si>
+    <t>kucev</t>
+  </si>
+  <si>
+    <t>2025-04-24T11:00:48.000Z</t>
+  </si>
+  <si>
+    <t>Data Mining * Искусственный интеллектМашинное обучение * Big Data * Data Engineering *, Data Mining * Искусственный интеллектМашинное обучение * Big Data * Data Engineering *, Data Mining *, Data Mining *, *, Искусственный интеллект, Искусственный интеллект, Машинное обучение *, Машинное обучение *, *, Big Data *, Big Data *, *, Data Engineering *, Data Engineering *, *, Data Mining, Искусственный интеллект, Машинное обучение, Big Data, Data Engineering</t>
+  </si>
+  <si>
+    <t>Теги:ai agentai agentsии-агентыai агентыaiииllm, ai agent, ai agents, ии-агенты, ai агенты, ai, ии, llm</t>
   </si>
   <si>
     <t>Парадокс Ньюкома и искусственный интеллект</t>
@@ -216,27 +240,54 @@
     <t>Теги:иипарадоксы, ии, парадоксы</t>
   </si>
   <si>
-    <t>Как тестировать AI-агентов, чтобы не было больно</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902598/</t>
-  </si>
-  <si>
-    <t>kucev</t>
-  </si>
-  <si>
-    <t>2025-04-24T11:00:48.000Z</t>
-  </si>
-  <si>
-    <t>Data Mining * Искусственный интеллектМашинное обучение * Big Data * Data Engineering *, Data Mining * Искусственный интеллектМашинное обучение * Big Data * Data Engineering *, Data Mining *, Data Mining *, *, Искусственный интеллект, Искусственный интеллект, Машинное обучение *, Машинное обучение *, *, Big Data *, Big Data *, *, Data Engineering *, Data Engineering *, *, Data Mining, Искусственный интеллект, Машинное обучение, Big Data, Data Engineering</t>
-  </si>
-  <si>
-    <t>Теги:ai agentai agentsии-агентыai агентыaiииllm, ai agent, ai agents, ии-агенты, ai агенты, ai, ии, llm</t>
-  </si>
-  <si>
     <t>docker контейнеризация</t>
   </si>
   <si>
+    <t>Как интеграция поддержки виртуализации VMware меняет подход к контейнеризации</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/903924/</t>
+  </si>
+  <si>
+    <t>dbraincloud</t>
+  </si>
+  <si>
+    <t>2025-04-29T07:19:24.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании dBrainВиртуализация * IT-инфраструктура * DevOps * Kubernetes *, Блог компании dBrainВиртуализация * IT-инфраструктура * DevOps * Kubernetes *, Блог компании dBrain, Блог компании dBrain, Виртуализация *, Виртуализация *, *, IT-инфраструктура *, IT-инфраструктура *, *, DevOps *, DevOps *, *, Kubernetes *, Kubernetes *, *, Блог компании dBrain, Виртуализация, IT-инфраструктура, DevOps, Kubernetes</t>
+  </si>
+  <si>
+    <t>Теги:виртуализациявиртуальная машинаконтейнеризациягипервизорbare-metalhostdbrainvmwarekubernetesмикросервисы, виртуализация, виртуальная машина, контейнеризация, гипервизор, bare-metal, host, dbrain, vmware, kubernetes, микросервисы</t>
+  </si>
+  <si>
+    <t>Платформа контейнеризации dBrain проходит сертификацию ФСТЭК</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/905796/</t>
+  </si>
+  <si>
+    <t>2025-04-30T06:55:54.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании dBrainМикросервисы * DevOps * IT-инфраструктура * Kubernetes *, Блог компании dBrainМикросервисы * DevOps * IT-инфраструктура * Kubernetes *, Блог компании dBrain, Блог компании dBrain, Микросервисы *, Микросервисы *, *, DevOps *, DevOps *, *, IT-инфраструктура *, IT-инфраструктура *, *, Kubernetes *, Kubernetes *, *, Блог компании dBrain, Микросервисы, DevOps, IT-инфраструктура, Kubernetes</t>
+  </si>
+  <si>
+    <t>Теги:kubernetesdevopsфстэкфстэк россииконтейнеризациябезопасностьуязвимостиdbrainкиииспдн, kubernetes, devops, фстэк, фстэк россии, контейнеризация, безопасность, уязвимости, dbrain, кии, испдн</t>
+  </si>
+  <si>
+    <t>Моя попытка №2. Как мы тестировали совместимость платформы контейнеризации с Astra Linux</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/909582/</t>
+  </si>
+  <si>
+    <t>2025-05-15T07:07:12.000Z</t>
+  </si>
+  <si>
+    <t>Теги:микросервисытестированиеосоперационные системыalt linuxальтлинуксdbrainspecial editioncri-odebian, микросервисы, тестирование, ос, операционные системы, alt linux, альтлинукс, dbrain, special edition, cri-o, debian</t>
+  </si>
+  <si>
     <t>Docker отказывается от виртуализации QEMU в Docker Desktop для Mac</t>
   </si>
   <si>
@@ -255,22 +306,76 @@
     <t>Теги:dockerdocker desktopmacmacosqemuвиртуализациядокерсофт, docker, docker desktop, mac, macos, qemu, виртуализация, докер, софт</t>
   </si>
   <si>
-    <t>Платформа контейнеризации dBrain проходит сертификацию ФСТЭК</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/905796/</t>
-  </si>
-  <si>
-    <t>dbraincloud</t>
-  </si>
-  <si>
-    <t>2025-04-30T06:55:54.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании dBrainМикросервисы * DevOps * IT-инфраструктура * Kubernetes *, Блог компании dBrainМикросервисы * DevOps * IT-инфраструктура * Kubernetes *, Блог компании dBrain, Блог компании dBrain, Микросервисы *, Микросервисы *, *, DevOps *, DevOps *, *, IT-инфраструктура *, IT-инфраструктура *, *, Kubernetes *, Kubernetes *, *, Блог компании dBrain, Микросервисы, DevOps, IT-инфраструктура, Kubernetes</t>
-  </si>
-  <si>
-    <t>Теги:kubernetesdevopsфстэкфстэк россииконтейнеризациябезопасностьуязвимостиdbrainкиииспдн, kubernetes, devops, фстэк, фстэк россии, контейнеризация, безопасность, уязвимости, dbrain, кии, испдн</t>
+    <t>Знание контейнеров: путь к большим деньгам в ИТ или временный хайп?</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/909650/</t>
+  </si>
+  <si>
+    <t>ChislitelLab</t>
+  </si>
+  <si>
+    <t>2025-05-15T09:17:24.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании Лаборатория ЧислительIT-инфраструктура * Карьера в IT-индустрииDevOps * Kubernetes *, Блог компании Лаборатория ЧислительIT-инфраструктура * Карьера в IT-индустрииDevOps * Kubernetes *, Блог компании Лаборатория Числитель, Блог компании Лаборатория Числитель, IT-инфраструктура *, IT-инфраструктура *, *, Карьера в IT-индустрии, Карьера в IT-индустрии, DevOps *, DevOps *, *, Kubernetes *, Kubernetes *, *, Блог компании Лаборатория Числитель, IT-инфраструктура, Карьера в IT-индустрии, DevOps, Kubernetes</t>
+  </si>
+  <si>
+    <t>Теги:контейнеризацияkubernetesdockerk8sконтейнерысофткарьера в иткарьера в ит-индустрииit-конференцииdevops, контейнеризация, kubernetes, docker, k8s, контейнеры, софт, карьера в ит, карьера в ит-индустрии, it-конференции, devops</t>
+  </si>
+  <si>
+    <t>Приложение Docker Desktop стало доступно в Microsoft Store</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/907486/</t>
+  </si>
+  <si>
+    <t>darya_kiwi</t>
+  </si>
+  <si>
+    <t>2025-05-07T05:14:58.000Z</t>
+  </si>
+  <si>
+    <t>СофтWindows * Виртуализация * Системное администрирование * Серверное администрирование *, СофтWindows * Виртуализация * Системное администрирование * Серверное администрирование *, Софт, Софт, Windows *, Windows *, *, Виртуализация *, Виртуализация *, *, Системное администрирование *, Системное администрирование *, *, Серверное администрирование *, Серверное администрирование *, *, Софт, Windows, Виртуализация, Системное администрирование, Серверное администрирование</t>
+  </si>
+  <si>
+    <t>Теги:docker desktopwindowsmicrosoft store, docker desktop, windows, microsoft store</t>
+  </si>
+  <si>
+    <t>Telegram бот управления Docker контейнерами</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/908894/</t>
+  </si>
+  <si>
+    <t>aleksxx</t>
+  </si>
+  <si>
+    <t>2025-09-16T10:41:21.000Z</t>
+  </si>
+  <si>
+    <t>*nix * Python * DevOps *, *nix * Python * DevOps *, *nix *, *nix *, *, Python *, Python *, *, DevOps *, DevOps *, *, *nix, Python, DevOps</t>
+  </si>
+  <si>
+    <t>Теги:fastapitelegrambotdocker, fastapi, telegrambot, docker</t>
+  </si>
+  <si>
+    <t>Selectel выпустил бесплатный курс по Docker</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/903226/</t>
+  </si>
+  <si>
+    <t>DimDimDimDimDim</t>
+  </si>
+  <si>
+    <t>2025-04-22T12:07:06.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании SelectelIT-компанииКарьера в IT-индустрииПрограммирование * Учебный процесс в IT, Блог компании SelectelIT-компанииКарьера в IT-индустрииПрограммирование * Учебный процесс в IT, Блог компании Selectel, Блог компании Selectel, IT-компании, IT-компании, Карьера в IT-индустрии, Карьера в IT-индустрии, Программирование *, Программирование *, *, Учебный процесс в IT, Учебный процесс в IT, Блог компании Selectel, IT-компании, Карьера в IT-индустрии, Программирование, Учебный процесс в IT</t>
+  </si>
+  <si>
+    <t>Теги:selectelкурсыбесплатные курсыdocker, selectel, курсы, бесплатные курсы, docker</t>
   </si>
   <si>
     <t>Команда Docker выпустила плагин Docker DX для VS Code</t>
@@ -288,105 +393,6 @@
     <t>Теги:dockerdocker dxvs codeредактор кодаплагинсофтинструменты, docker, docker dx, vs code, редактор кода, плагин, софт, инструменты</t>
   </si>
   <si>
-    <t>Как интеграция поддержки виртуализации VMware меняет подход к контейнеризации</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/903924/</t>
-  </si>
-  <si>
-    <t>2025-04-29T07:19:24.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании dBrainВиртуализация * IT-инфраструктура * DevOps * Kubernetes *, Блог компании dBrainВиртуализация * IT-инфраструктура * DevOps * Kubernetes *, Блог компании dBrain, Блог компании dBrain, Виртуализация *, Виртуализация *, *, IT-инфраструктура *, IT-инфраструктура *, *, DevOps *, DevOps *, *, Kubernetes *, Kubernetes *, *, Блог компании dBrain, Виртуализация, IT-инфраструктура, DevOps, Kubernetes</t>
-  </si>
-  <si>
-    <t>Теги:виртуализациявиртуальная машинаконтейнеризациягипервизорbare-metalhostdbrainvmwarekubernetesмикросервисы, виртуализация, виртуальная машина, контейнеризация, гипервизор, bare-metal, host, dbrain, vmware, kubernetes, микросервисы</t>
-  </si>
-  <si>
-    <t>Моя попытка №2. Как мы тестировали совместимость платформы контейнеризации с Astra Linux</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/909582/</t>
-  </si>
-  <si>
-    <t>2025-05-15T07:07:12.000Z</t>
-  </si>
-  <si>
-    <t>Теги:микросервисытестированиеосоперационные системыalt linuxальтлинуксdbrainspecial editioncri-odebian, микросервисы, тестирование, ос, операционные системы, alt linux, альтлинукс, dbrain, special edition, cri-o, debian</t>
-  </si>
-  <si>
-    <t>Selectel выпустил бесплатный курс по Docker</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/903226/</t>
-  </si>
-  <si>
-    <t>DimDimDimDimDim</t>
-  </si>
-  <si>
-    <t>2025-04-22T12:07:06.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании SelectelIT-компанииКарьера в IT-индустрииПрограммирование * Учебный процесс в IT, Блог компании SelectelIT-компанииКарьера в IT-индустрииПрограммирование * Учебный процесс в IT, Блог компании Selectel, Блог компании Selectel, IT-компании, IT-компании, Карьера в IT-индустрии, Карьера в IT-индустрии, Программирование *, Программирование *, *, Учебный процесс в IT, Учебный процесс в IT, Блог компании Selectel, IT-компании, Карьера в IT-индустрии, Программирование, Учебный процесс в IT</t>
-  </si>
-  <si>
-    <t>Теги:selectelкурсыбесплатные курсыdocker, selectel, курсы, бесплатные курсы, docker</t>
-  </si>
-  <si>
-    <t>Telegram бот управления Docker контейнерами</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/908894/</t>
-  </si>
-  <si>
-    <t>aleksxx</t>
-  </si>
-  <si>
-    <t>2025-09-16T10:41:21.000Z</t>
-  </si>
-  <si>
-    <t>*nix * Python * DevOps *, *nix * Python * DevOps *, *nix *, *nix *, *, Python *, Python *, *, DevOps *, DevOps *, *, *nix, Python, DevOps</t>
-  </si>
-  <si>
-    <t>Теги:fastapitelegrambotdocker, fastapi, telegrambot, docker</t>
-  </si>
-  <si>
-    <t>Знание контейнеров: путь к большим деньгам в ИТ или временный хайп?</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/909650/</t>
-  </si>
-  <si>
-    <t>ChislitelLab</t>
-  </si>
-  <si>
-    <t>2025-05-15T09:17:24.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании Лаборатория ЧислительIT-инфраструктура * Карьера в IT-индустрииDevOps * Kubernetes *, Блог компании Лаборатория ЧислительIT-инфраструктура * Карьера в IT-индустрииDevOps * Kubernetes *, Блог компании Лаборатория Числитель, Блог компании Лаборатория Числитель, IT-инфраструктура *, IT-инфраструктура *, *, Карьера в IT-индустрии, Карьера в IT-индустрии, DevOps *, DevOps *, *, Kubernetes *, Kubernetes *, *, Блог компании Лаборатория Числитель, IT-инфраструктура, Карьера в IT-индустрии, DevOps, Kubernetes</t>
-  </si>
-  <si>
-    <t>Теги:контейнеризацияkubernetesdockerk8sконтейнерысофткарьера в иткарьера в ит-индустрииit-конференцииdevops, контейнеризация, kubernetes, docker, k8s, контейнеры, софт, карьера в ит, карьера в ит-индустрии, it-конференции, devops</t>
-  </si>
-  <si>
-    <t>Приложение Docker Desktop стало доступно в Microsoft Store</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/907486/</t>
-  </si>
-  <si>
-    <t>darya_kiwi</t>
-  </si>
-  <si>
-    <t>2025-05-07T05:14:58.000Z</t>
-  </si>
-  <si>
-    <t>СофтWindows * Виртуализация * Системное администрирование * Серверное администрирование *, СофтWindows * Виртуализация * Системное администрирование * Серверное администрирование *, Софт, Софт, Windows *, Windows *, *, Виртуализация *, Виртуализация *, *, Системное администрирование *, Системное администрирование *, *, Серверное администрирование *, Серверное администрирование *, *, Софт, Windows, Виртуализация, Системное администрирование, Серверное администрирование</t>
-  </si>
-  <si>
-    <t>Теги:docker desktopwindowsmicrosoft store, docker desktop, windows, microsoft store</t>
-  </si>
-  <si>
     <t>Погружение в grammY: разработка Telegram-бота с TypeScript и Docker</t>
   </si>
   <si>
@@ -411,6 +417,87 @@
     <t>веб разработка frontend</t>
   </si>
   <si>
+    <t>Веб-разработка на ванильном HTML, CSS и JavaScript</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/909390/</t>
+  </si>
+  <si>
+    <t>ru_vds</t>
+  </si>
+  <si>
+    <t>2025-05-14T13:01:59.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании RUVDS.comCSS * HTML * JavaScript * Веб-разработка *, Блог компании RUVDS.comCSS * HTML * JavaScript * Веб-разработка *, Блог компании RUVDS.com, Блог компании RUVDS.com, CSS *, CSS *, *, HTML *, HTML *, *, JavaScript *, JavaScript *, *, Веб-разработка *, Веб-разработка *, *, Блог компании RUVDS.com, CSS, HTML, JavaScript, Веб-разработка</t>
+  </si>
+  <si>
+    <t>Теги:ruvds_переводывеб-компонентыcustom elementsshadow domhtml шаблон, ruvds_переводы, веб-компоненты, custom elements, shadow dom, html шаблон</t>
+  </si>
+  <si>
+    <t>Веб-разработка на ванильном HTML, CSS и JavaScript: стилизация и сайты</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/910734/</t>
+  </si>
+  <si>
+    <t>2025-05-19T13:01:01.000Z</t>
+  </si>
+  <si>
+    <t>Асинхронность в JavaScript, как использовать в web разработке на React, цепочка промисов и параллельное выполнение</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/910462/</t>
+  </si>
+  <si>
+    <t>SergeySeredkinlipetsk</t>
+  </si>
+  <si>
+    <t>2025-05-19T19:04:59.000Z</t>
+  </si>
+  <si>
+    <t>HabrJavaScript * NestJS * PostgreSQL * ReactJS *, HabrJavaScript * NestJS * PostgreSQL * ReactJS *, Habr, Habr, JavaScript *, JavaScript *, *, NestJS *, NestJS *, *, PostgreSQL *, PostgreSQL *, *, ReactJS *, ReactJS *, *, Habr, JavaScript, NestJS, PostgreSQL, ReactJS</t>
+  </si>
+  <si>
+    <t>Теги:reactpromiseaxiosnext.jspostgresbackend, react, promise, axios, next.js, postgres, backend</t>
+  </si>
+  <si>
+    <t>Книга: «RESTful Web API: Паттерны и практики»</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902070/</t>
+  </si>
+  <si>
+    <t>ph_piter</t>
+  </si>
+  <si>
+    <t>2025-04-29T12:29:23.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании Издательский дом «Питер»Проектирование API * Анализ и проектирование систем * Профессиональная литература *, Блог компании Издательский дом «Питер»Проектирование API * Анализ и проектирование систем * Профессиональная литература *, Блог компании Издательский дом «Питер», Блог компании Издательский дом «Питер», Проектирование API *, Проектирование API *, *, Анализ и проектирование систем *, Анализ и проектирование систем *, *, Профессиональная литература *, Профессиональная литература *, *, Блог компании Издательский дом «Питер», Проектирование API, Анализ и проектирование систем, Профессиональная литература</t>
+  </si>
+  <si>
+    <t>Теги:книга, книга</t>
+  </si>
+  <si>
+    <t>Знакомство с Web Locks API</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/901822/</t>
+  </si>
+  <si>
+    <t>yadobr</t>
+  </si>
+  <si>
+    <t>2025-04-18T07:56:42.000Z</t>
+  </si>
+  <si>
+    <t>JavaScript * Программирование * Веб-разработка * TypeScript * Интерфейсы *, JavaScript * Программирование * Веб-разработка * TypeScript * Интерфейсы *, JavaScript *, JavaScript *, *, Программирование *, Программирование *, *, Веб-разработка *, Веб-разработка *, *, TypeScript *, TypeScript *, *, Интерфейсы *, Интерфейсы *, *, JavaScript, Программирование, Веб-разработка, TypeScript, Интерфейсы</t>
+  </si>
+  <si>
+    <t>Теги:javascriptfrontendfrontend-разработкавеб-разработаtypescriptweb locks apistorage-eventlocalstoragesessionstoragebroadcast channel, javascript, frontend, frontend-разработка, веб-разработа, typescript, web locks api, storage-event, localstorage, sessionstorage, broadcast channel</t>
+  </si>
+  <si>
     <t>Netter как способ упрощения разработки веб серверов</t>
   </si>
   <si>
@@ -429,33 +516,6 @@
     <t>Теги:rusthttpweb-serverhttpscli, rust, http, web-server, https, cli</t>
   </si>
   <si>
-    <t>Веб-разработка на ванильном HTML, CSS и JavaScript</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/909390/</t>
-  </si>
-  <si>
-    <t>ru_vds</t>
-  </si>
-  <si>
-    <t>2025-05-14T13:01:59.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании RUVDS.comCSS * HTML * JavaScript * Веб-разработка *, Блог компании RUVDS.comCSS * HTML * JavaScript * Веб-разработка *, Блог компании RUVDS.com, Блог компании RUVDS.com, CSS *, CSS *, *, HTML *, HTML *, *, JavaScript *, JavaScript *, *, Веб-разработка *, Веб-разработка *, *, Блог компании RUVDS.com, CSS, HTML, JavaScript, Веб-разработка</t>
-  </si>
-  <si>
-    <t>Теги:ruvds_переводывеб-компонентыcustom elementsshadow domhtml шаблон, ruvds_переводы, веб-компоненты, custom elements, shadow dom, html шаблон</t>
-  </si>
-  <si>
-    <t>Веб-разработка на ванильном HTML, CSS и JavaScript: стилизация и сайты</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/910734/</t>
-  </si>
-  <si>
-    <t>2025-05-19T13:01:01.000Z</t>
-  </si>
-  <si>
     <t>«Сети Судного дня». Как разработка противоядерной ПВО привела к рождению Интернета?</t>
   </si>
   <si>
@@ -474,58 +534,22 @@
     <t>Теги:ruvds_статьи_выходного_дняисторияarpanetsageалданс-25darpaarpa, ruvds_статьи_выходного_дня, история, arpanet, sage, алдан, с-25, darpa, arpa</t>
   </si>
   <si>
-    <t>Асинхронность в JavaScript, как использовать в web разработке на React, цепочка промисов и параллельное выполнение</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/910462/</t>
-  </si>
-  <si>
-    <t>SergeySeredkinlipetsk</t>
-  </si>
-  <si>
-    <t>2025-05-19T19:04:59.000Z</t>
-  </si>
-  <si>
-    <t>HabrJavaScript * NestJS * PostgreSQL * ReactJS *, HabrJavaScript * NestJS * PostgreSQL * ReactJS *, Habr, Habr, JavaScript *, JavaScript *, *, NestJS *, NestJS *, *, PostgreSQL *, PostgreSQL *, *, ReactJS *, ReactJS *, *, Habr, JavaScript, NestJS, PostgreSQL, ReactJS</t>
-  </si>
-  <si>
-    <t>Теги:reactpromiseaxiosnext.jspostgresbackend, react, promise, axios, next.js, postgres, backend</t>
-  </si>
-  <si>
-    <t>Знакомство с Web Locks API</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/901822/</t>
-  </si>
-  <si>
-    <t>yadobr</t>
-  </si>
-  <si>
-    <t>2025-04-18T07:56:42.000Z</t>
-  </si>
-  <si>
-    <t>JavaScript * Программирование * Веб-разработка * TypeScript * Интерфейсы *, JavaScript * Программирование * Веб-разработка * TypeScript * Интерфейсы *, JavaScript *, JavaScript *, *, Программирование *, Программирование *, *, Веб-разработка *, Веб-разработка *, *, TypeScript *, TypeScript *, *, Интерфейсы *, Интерфейсы *, *, JavaScript, Программирование, Веб-разработка, TypeScript, Интерфейсы</t>
-  </si>
-  <si>
-    <t>Теги:javascriptfrontendfrontend-разработкавеб-разработаtypescriptweb locks apistorage-eventlocalstoragesessionstoragebroadcast channel, javascript, frontend, frontend-разработка, веб-разработа, typescript, web locks api, storage-event, localstorage, sessionstorage, broadcast channel</t>
-  </si>
-  <si>
-    <t>Книга: «RESTful Web API: Паттерны и практики»</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902070/</t>
-  </si>
-  <si>
-    <t>ph_piter</t>
-  </si>
-  <si>
-    <t>2025-04-29T12:29:23.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании Издательский дом «Питер»Проектирование API * Анализ и проектирование систем * Профессиональная литература *, Блог компании Издательский дом «Питер»Проектирование API * Анализ и проектирование систем * Профессиональная литература *, Блог компании Издательский дом «Питер», Блог компании Издательский дом «Питер», Проектирование API *, Проектирование API *, *, Анализ и проектирование систем *, Анализ и проектирование систем *, *, Профессиональная литература *, Профессиональная литература *, *, Блог компании Издательский дом «Питер», Проектирование API, Анализ и проектирование систем, Профессиональная литература</t>
-  </si>
-  <si>
-    <t>Теги:книга, книга</t>
+    <t>Почему не дружат фронтендер и дизайнер: работающие техники общения между отделами</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/909032/</t>
+  </si>
+  <si>
+    <t>Wannabenormal</t>
+  </si>
+  <si>
+    <t>2025-05-13T13:12:06.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании AGIMAУправление разработкой * ДизайнВеб-разработка * Веб-дизайн *, Блог компании AGIMAУправление разработкой * ДизайнВеб-разработка * Веб-дизайн *, Блог компании AGIMA, Блог компании AGIMA, Управление разработкой *, Управление разработкой *, *, Дизайн, Дизайн, Веб-разработка *, Веб-разработка *, *, Веб-дизайн *, Веб-дизайн *, *, Блог компании AGIMA, Управление разработкой, Дизайн, Веб-разработка, Веб-дизайн</t>
+  </si>
+  <si>
+    <t>Теги:frontend-разработкадизайнуправление разработкойweb-разработкаweb-дизайнui kitfigma, frontend-разработка, дизайн, управление разработкой, web-разработка, web-дизайн, ui kit, figma</t>
   </si>
   <si>
     <t>Anthropic запускает API для веб-поиска на базе AI</t>
@@ -558,27 +582,63 @@
     <t>Теги:веб-разработапрограммированиеbackendfrontendалгоритмыархитектура, веб-разработа, программирование, backend, frontend, алгоритмы, архитектура</t>
   </si>
   <si>
-    <t>Почему не дружат фронтендер и дизайнер: работающие техники общения между отделами</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/909032/</t>
-  </si>
-  <si>
-    <t>Wannabenormal</t>
-  </si>
-  <si>
-    <t>2025-05-13T13:12:06.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании AGIMAУправление разработкой * ДизайнВеб-разработка * Веб-дизайн *, Блог компании AGIMAУправление разработкой * ДизайнВеб-разработка * Веб-дизайн *, Блог компании AGIMA, Блог компании AGIMA, Управление разработкой *, Управление разработкой *, *, Дизайн, Дизайн, Веб-разработка *, Веб-разработка *, *, Веб-дизайн *, Веб-дизайн *, *, Блог компании AGIMA, Управление разработкой, Дизайн, Веб-разработка, Веб-дизайн</t>
-  </si>
-  <si>
-    <t>Теги:frontend-разработкадизайнуправление разработкойweb-разработкаweb-дизайнui kitfigma, frontend-разработка, дизайн, управление разработкой, web-разработка, web-дизайн, ui kit, figma</t>
-  </si>
-  <si>
     <t>база данных SQL</t>
   </si>
   <si>
+    <t>LLM пайплайны укрощают сложность баз данных, или как мы подружили ИИ с БД без ИБД</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/907614/</t>
+  </si>
+  <si>
+    <t>Safreliy</t>
+  </si>
+  <si>
+    <t>2025-05-07T18:20:10.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании Postgres ProfessionalИскусственный интеллектМашинное обучение * SQL * PostgreSQL *, Блог компании Postgres ProfessionalИскусственный интеллектМашинное обучение * SQL * PostgreSQL *, Блог компании Postgres Professional, Блог компании Postgres Professional, Искусственный интеллект, Искусственный интеллект, Машинное обучение *, Машинное обучение *, *, SQL *, SQL *, *, PostgreSQL *, PostgreSQL *, *, Блог компании Postgres Professional, Искусственный интеллект, Машинное обучение, SQL, PostgreSQL</t>
+  </si>
+  <si>
+    <t>Теги:генерация sqlгенерация cypherragсубдискусственный интеллектsqlcypherpostgresqlгенерация кодаllm-агент, генерация sql, генерация cypher, rag, субд, искусственный интеллект, sql, cypher, postgresql, генерация кода, llm-агент</t>
+  </si>
+  <si>
+    <t>JDBC: Как Java научилась дружить с Базами Данных</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902240/</t>
+  </si>
+  <si>
+    <t>MaxRokatansky</t>
+  </si>
+  <si>
+    <t>2025-04-19T14:13:59.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании OTUSБазы данных * Java *, Блог компании OTUSБазы данных * Java *, Блог компании OTUS, Блог компании OTUS, Базы данных *, Базы данных *, *, Java *, Java *, *, Блог компании OTUS, Базы данных, Java</t>
+  </si>
+  <si>
+    <t>Теги:jdbcjavaбазы данныхsql-инъекциитранзакциихранимые процедурысубд, jdbc, java, базы данных, sql-инъекции, транзакции, хранимые процедуры, субд</t>
+  </si>
+  <si>
+    <t>Индексы в базах данных: сколько индексов — перебор?</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/907600/</t>
+  </si>
+  <si>
+    <t>Daria_Chetyrkina</t>
+  </si>
+  <si>
+    <t>2025-05-07T09:53:44.000Z</t>
+  </si>
+  <si>
+    <t>SQL * Microsoft SQL Server *, SQL * Microsoft SQL Server *, SQL *, SQL *, *, Microsoft SQL Server *, Microsoft SQL Server *, *, SQL, Microsoft SQL Server</t>
+  </si>
+  <si>
+    <t>Теги:SQLиндексы, SQL, индексы</t>
+  </si>
+  <si>
     <t>Как LLM могут помочь аналитикам баз данных в работе с SQL-запросами</t>
   </si>
   <si>
@@ -597,58 +657,37 @@
     <t>Теги:LLMsql, LLM, sql</t>
   </si>
   <si>
-    <t>LLM пайплайны укрощают сложность баз данных, или как мы подружили ИИ с БД без ИБД</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/907614/</t>
-  </si>
-  <si>
-    <t>Safreliy</t>
-  </si>
-  <si>
-    <t>2025-05-07T18:20:10.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании Postgres ProfessionalИскусственный интеллектМашинное обучение * SQL * PostgreSQL *, Блог компании Postgres ProfessionalИскусственный интеллектМашинное обучение * SQL * PostgreSQL *, Блог компании Postgres Professional, Блог компании Postgres Professional, Искусственный интеллект, Искусственный интеллект, Машинное обучение *, Машинное обучение *, *, SQL *, SQL *, *, PostgreSQL *, PostgreSQL *, *, Блог компании Postgres Professional, Искусственный интеллект, Машинное обучение, SQL, PostgreSQL</t>
-  </si>
-  <si>
-    <t>Теги:генерация sqlгенерация cypherragсубдискусственный интеллектsqlcypherpostgresqlгенерация кодаllm-агент, генерация sql, генерация cypher, rag, субд, искусственный интеллект, sql, cypher, postgresql, генерация кода, llm-агент</t>
-  </si>
-  <si>
-    <t>JDBC: Как Java научилась дружить с Базами Данных</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902240/</t>
-  </si>
-  <si>
-    <t>MaxRokatansky</t>
-  </si>
-  <si>
-    <t>2025-04-19T14:13:59.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании OTUSБазы данных * Java *, Блог компании OTUSБазы данных * Java *, Блог компании OTUS, Блог компании OTUS, Базы данных *, Базы данных *, *, Java *, Java *, *, Блог компании OTUS, Базы данных, Java</t>
-  </si>
-  <si>
-    <t>Теги:jdbcjavaбазы данныхsql-инъекциитранзакциихранимые процедурысубд, jdbc, java, базы данных, sql-инъекции, транзакции, хранимые процедуры, субд</t>
-  </si>
-  <si>
-    <t>Индексы в базах данных: сколько индексов — перебор?</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/907600/</t>
-  </si>
-  <si>
-    <t>Daria_Chetyrkina</t>
-  </si>
-  <si>
-    <t>2025-05-07T09:53:44.000Z</t>
-  </si>
-  <si>
-    <t>SQL * Microsoft SQL Server *, SQL * Microsoft SQL Server *, SQL *, SQL *, *, Microsoft SQL Server *, Microsoft SQL Server *, *, SQL, Microsoft SQL Server</t>
-  </si>
-  <si>
-    <t>Теги:SQLиндексы, SQL, индексы</t>
+    <t>Работа с базой данных для джунов и вайбкодеров. Соединения</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/908376/</t>
+  </si>
+  <si>
+    <t>nvantropov</t>
+  </si>
+  <si>
+    <t>2025-05-11T15:20:33.000Z</t>
+  </si>
+  <si>
+    <t>Java * PostgreSQL * Node.JS * Go *, Java * PostgreSQL * Node.JS * Go *, Java *, Java *, *, PostgreSQL *, PostgreSQL *, *, Node.JS *, Node.JS *, *, Go *, Go *, *, Java, PostgreSQL, Node.JS, Go</t>
+  </si>
+  <si>
+    <t>Теги:базы данныхконнектыбагиконнект к бдпул соединенийhikaricphikaripoolpgbouncer, базы данных, коннекты, баги, коннект к бд, пул соединений, hikaricp, hikaripool, pgbouncer</t>
+  </si>
+  <si>
+    <t>5 главных критериев выбора инструмента для мониторинга баз данных</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/906874/</t>
+  </si>
+  <si>
+    <t>2025-05-05T06:36:19.000Z</t>
+  </si>
+  <si>
+    <t>Базы данных *, Базы данных *, Базы данных *, Базы данных *, *, Базы данных</t>
+  </si>
+  <si>
+    <t>Теги:база данных, база данных</t>
   </si>
   <si>
     <t>Вклад в склад: оптимизация запасов на базе данных</t>
@@ -669,24 +708,6 @@
     <t>Теги:управление запасамиуправление складомоптимизация запасоввебинар, управление запасами, управление складом, оптимизация запасов, вебинар</t>
   </si>
   <si>
-    <t>Работа с базой данных для джунов и вайбкодеров. Соединения</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/908376/</t>
-  </si>
-  <si>
-    <t>nvantropov</t>
-  </si>
-  <si>
-    <t>2025-05-11T15:20:33.000Z</t>
-  </si>
-  <si>
-    <t>Java * PostgreSQL * Node.JS * Go *, Java * PostgreSQL * Node.JS * Go *, Java *, Java *, *, PostgreSQL *, PostgreSQL *, *, Node.JS *, Node.JS *, *, Go *, Go *, *, Java, PostgreSQL, Node.JS, Go</t>
-  </si>
-  <si>
-    <t>Теги:базы данныхконнектыбагиконнект к бдпул соединенийhikaricphikaripoolpgbouncer, базы данных, коннекты, баги, коннект к бд, пул соединений, hikaricp, hikaripool, pgbouncer</t>
-  </si>
-  <si>
     <t>Стоимостной оптимизатор: сердце гибридной базы данных YDB</t>
   </si>
   <si>
@@ -741,21 +762,6 @@
     <t>Теги:vas expertscvegcveбдуeuvdинформационная безопасность, vas experts, cve, gcve, бду, euvd, информационная безопасность</t>
   </si>
   <si>
-    <t>5 главных критериев выбора инструмента для мониторинга баз данных</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/906874/</t>
-  </si>
-  <si>
-    <t>2025-05-05T06:36:19.000Z</t>
-  </si>
-  <si>
-    <t>Базы данных *, Базы данных *, Базы данных *, Базы данных *, *, Базы данных</t>
-  </si>
-  <si>
-    <t>Теги:база данных, база данных</t>
-  </si>
-  <si>
     <t>пайтон программирование</t>
   </si>
   <si>
@@ -795,6 +801,93 @@
     <t>Теги:pythonсистемный администраторпрограммирование, python, системный администратор, программирование</t>
   </si>
   <si>
+    <t>Game Engine 3 — оболочка для визуального программирования игр на Python (от идеи до реализации)</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902426/</t>
+  </si>
+  <si>
+    <t>artyom7777</t>
+  </si>
+  <si>
+    <t>2025-04-20T06:16:16.000Z</t>
+  </si>
+  <si>
+    <t>Python * Разработка игр * Open source * Программирование * Визуальное программирование *, Python * Разработка игр * Open source * Программирование * Визуальное программирование *, Python *, Python *, *, Разработка игр *, Разработка игр *, *, Open source *, Open source *, *, Программирование *, Программирование *, *, Визуальное программирование *, Визуальное программирование *, *, Python, Разработка игр, Open source, Программирование, Визуальное программирование</t>
+  </si>
+  <si>
+    <t>Теги:pythongame enginevisual programmingopen sourceсезон open sourcegame devвизуальное программированиеигровой движокразработка игрразработка приложений, python, game engine, visual programming, open source, сезон open source, game dev, визуальное программирование, игровой движок, разработка игр, разработка приложений</t>
+  </si>
+  <si>
+    <t>Псевдослучайный рандом в Python</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/907930/</t>
+  </si>
+  <si>
+    <t>leenakwa</t>
+  </si>
+  <si>
+    <t>2025-05-08T13:38:39.000Z</t>
+  </si>
+  <si>
+    <t>Python * Программирование * Алгоритмы * Научно-популярное, Python * Программирование * Алгоритмы * Научно-популярное, Python *, Python *, *, Программирование *, Программирование *, *, Алгоритмы *, Алгоритмы *, *, Научно-популярное, Научно-популярное, Python, Программирование, Алгоритмы, Научно-популярное</t>
+  </si>
+  <si>
+    <t>Теги:randomrandom number generatorпсевдослучайные числапитонрандом, random, random number generator, псевдослучайные числа, питон, рандом</t>
+  </si>
+  <si>
+    <t>Гравитация: Пишем симулятор на Python</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/908952/</t>
+  </si>
+  <si>
+    <t>Nikuson</t>
+  </si>
+  <si>
+    <t>2025-05-13T09:16:48.000Z</t>
+  </si>
+  <si>
+    <t>ФизикаPython * Визуализация данных * Интерфейсы *, ФизикаPython * Визуализация данных * Интерфейсы *, Физика, Физика, Python *, Python *, *, Визуализация данных *, Визуализация данных *, *, Интерфейсы *, Интерфейсы *, *, Физика, Python, Визуализация данных, Интерфейсы</t>
+  </si>
+  <si>
+    <t>Теги:гравитациясимуляцияpythonновичкамвизуализациярасчетыпрограммирование, гравитация, симуляция, python, новичкам, визуализация, расчеты, программирование</t>
+  </si>
+  <si>
+    <t>Сравнение Go и Python для веб-скрейпинга</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/900972/</t>
+  </si>
+  <si>
+    <t>2025-04-16T10:28:26.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании Издательский дом «Питер»Go * Python *, Блог компании Издательский дом «Питер»Go * Python *, Блог компании Издательский дом «Питер», Блог компании Издательский дом «Питер», Go *, Go *, *, Python *, Python *, *, Блог компании Издательский дом «Питер», Go, Python</t>
+  </si>
+  <si>
+    <t>Теги:переводвеб-программирование, перевод, веб-программирование</t>
+  </si>
+  <si>
+    <t>Декораторы Python. Продвинутое использование</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/910424/</t>
+  </si>
+  <si>
+    <t>Extralait</t>
+  </si>
+  <si>
+    <t>2025-05-18T13:45:22.000Z</t>
+  </si>
+  <si>
+    <t>Python * Программирование * Веб-разработка *, Python * Программирование * Веб-разработка *, Python *, Python *, *, Программирование *, Программирование *, *, Веб-разработка *, Веб-разработка *, *, Python, Программирование, Веб-разработка</t>
+  </si>
+  <si>
+    <t>Теги:pythonpython3decoratorдекоратордекораторыdecoratorsпрограммированиесигнатура, python, python3, decorator, декоратор, декораторы, decorators, программирование, сигнатура</t>
+  </si>
+  <si>
     <t>Python, Java, C++ и Go — как появились популярные языки программирования</t>
   </si>
   <si>
@@ -813,40 +906,22 @@
     <t>Теги:selectelязыки программированияpythongorustphpc#c++javascript, selectel, языки программирования, python, go, rust, php, c#, c++, javascript</t>
   </si>
   <si>
-    <t>Game Engine 3 — оболочка для визуального программирования игр на Python (от идеи до реализации)</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902426/</t>
-  </si>
-  <si>
-    <t>artyom7777</t>
-  </si>
-  <si>
-    <t>2025-04-20T06:16:16.000Z</t>
-  </si>
-  <si>
-    <t>Python * Разработка игр * Open source * Программирование * Визуальное программирование *, Python * Разработка игр * Open source * Программирование * Визуальное программирование *, Python *, Python *, *, Разработка игр *, Разработка игр *, *, Open source *, Open source *, *, Программирование *, Программирование *, *, Визуальное программирование *, Визуальное программирование *, *, Python, Разработка игр, Open source, Программирование, Визуальное программирование</t>
-  </si>
-  <si>
-    <t>Теги:pythongame enginevisual programmingopen sourceсезон open sourcegame devвизуальное программированиеигровой движокразработка игрразработка приложений, python, game engine, visual programming, open source, сезон open source, game dev, визуальное программирование, игровой движок, разработка игр, разработка приложений</t>
-  </si>
-  <si>
-    <t>Псевдослучайный рандом в Python</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/907930/</t>
-  </si>
-  <si>
-    <t>leenakwa</t>
-  </si>
-  <si>
-    <t>2025-05-08T13:38:39.000Z</t>
-  </si>
-  <si>
-    <t>Python * Программирование * Алгоритмы * Научно-популярное, Python * Программирование * Алгоритмы * Научно-популярное, Python *, Python *, *, Программирование *, Программирование *, *, Алгоритмы *, Алгоритмы *, *, Научно-популярное, Научно-популярное, Python, Программирование, Алгоритмы, Научно-популярное</t>
-  </si>
-  <si>
-    <t>Теги:randomrandom number generatorпсевдослучайные числапитонрандом, random, random number generator, псевдослучайные числа, питон, рандом</t>
+    <t>Qt for Python: PySide6</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/909118/</t>
+  </si>
+  <si>
+    <t>Andrey4ik</t>
+  </si>
+  <si>
+    <t>2025-05-13T15:45:44.000Z</t>
+  </si>
+  <si>
+    <t>Python * Qt * Windows * Linux * Интерфейсы *, Python * Qt * Windows * Linux * Интерфейсы *, Python *, Python *, *, Qt *, Qt *, *, Windows *, Windows *, *, Linux *, Linux *, *, Интерфейсы *, Интерфейсы *, *, Python, Qt, Windows, Linux, Интерфейсы</t>
+  </si>
+  <si>
+    <t>Теги:qtqt6pythonpython3pyside6pysidelinuxwindowsdevelopmentqt software, qt, qt6, python, python3, pyside6, pyside, linux, windows, development, qt software</t>
   </si>
   <si>
     <t>Python Day на PHDays — не только доклады</t>
@@ -864,75 +939,6 @@
     <t>Теги:phdayspythonспикерыcybersecurityвеб-фреймворкdiinnersource, phdays, python, спикеры, cybersecurity, веб-фреймворк, di, innersource</t>
   </si>
   <si>
-    <t>Гравитация: Пишем симулятор на Python</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/908952/</t>
-  </si>
-  <si>
-    <t>Nikuson</t>
-  </si>
-  <si>
-    <t>2025-05-13T09:16:48.000Z</t>
-  </si>
-  <si>
-    <t>ФизикаPython * Визуализация данных * Интерфейсы *, ФизикаPython * Визуализация данных * Интерфейсы *, Физика, Физика, Python *, Python *, *, Визуализация данных *, Визуализация данных *, *, Интерфейсы *, Интерфейсы *, *, Физика, Python, Визуализация данных, Интерфейсы</t>
-  </si>
-  <si>
-    <t>Теги:гравитациясимуляцияpythonновичкамвизуализациярасчетыпрограммирование, гравитация, симуляция, python, новичкам, визуализация, расчеты, программирование</t>
-  </si>
-  <si>
-    <t>Qt for Python: PySide6</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/909118/</t>
-  </si>
-  <si>
-    <t>Andrey4ik</t>
-  </si>
-  <si>
-    <t>2025-05-13T15:45:44.000Z</t>
-  </si>
-  <si>
-    <t>Python * Qt * Windows * Linux * Интерфейсы *, Python * Qt * Windows * Linux * Интерфейсы *, Python *, Python *, *, Qt *, Qt *, *, Windows *, Windows *, *, Linux *, Linux *, *, Интерфейсы *, Интерфейсы *, *, Python, Qt, Windows, Linux, Интерфейсы</t>
-  </si>
-  <si>
-    <t>Теги:qtqt6pythonpython3pyside6pysidelinuxwindowsdevelopmentqt software, qt, qt6, python, python3, pyside6, pyside, linux, windows, development, qt software</t>
-  </si>
-  <si>
-    <t>Декораторы Python. Продвинутое использование</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/910424/</t>
-  </si>
-  <si>
-    <t>Extralait</t>
-  </si>
-  <si>
-    <t>2025-05-18T13:45:22.000Z</t>
-  </si>
-  <si>
-    <t>Python * Программирование * Веб-разработка *, Python * Программирование * Веб-разработка *, Python *, Python *, *, Программирование *, Программирование *, *, Веб-разработка *, Веб-разработка *, *, Python, Программирование, Веб-разработка</t>
-  </si>
-  <si>
-    <t>Теги:pythonpython3decoratorдекоратордекораторыdecoratorsпрограммированиесигнатура, python, python3, decorator, декоратор, декораторы, decorators, программирование, сигнатура</t>
-  </si>
-  <si>
-    <t>Сравнение Go и Python для веб-скрейпинга</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/900972/</t>
-  </si>
-  <si>
-    <t>2025-04-16T10:28:26.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании Издательский дом «Питер»Go * Python *, Блог компании Издательский дом «Питер»Go * Python *, Блог компании Издательский дом «Питер», Блог компании Издательский дом «Питер», Go *, Go *, *, Python *, Python *, *, Блог компании Издательский дом «Питер», Go, Python</t>
-  </si>
-  <si>
-    <t>Теги:переводвеб-программирование, перевод, веб-программирование</t>
-  </si>
-  <si>
     <t>javascript фреймворки</t>
   </si>
   <si>
@@ -1134,6 +1140,57 @@
     <t>Теги:golangаллокация памятиуказателиструктурные типыgeneric-кодуправление памятью, golang, аллокация памяти, указатели, структурные типы, generic-код, управление памятью</t>
   </si>
   <si>
+    <t>Первый http сервер на С++, заметки для новичков</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/910222/</t>
+  </si>
+  <si>
+    <t>kkmspb</t>
+  </si>
+  <si>
+    <t>2025-05-17T16:59:47.000Z</t>
+  </si>
+  <si>
+    <t>PHP * JavaScript * C++ * Qt *, PHP * JavaScript * C++ * Qt *, PHP *, PHP *, *, JavaScript *, JavaScript *, *, C++ *, C++ *, *, Qt *, Qt *, *, PHP, JavaScript, C++, Qt</t>
+  </si>
+  <si>
+    <t>Теги:Content-Typeurlencodejsonbase64hex, Content-Type, urlencode, json, base64, hex</t>
+  </si>
+  <si>
+    <t>fit() для новичков</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/905858/</t>
+  </si>
+  <si>
+    <t>2025-05-16T12:05:01.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании OTUSМашинное обучение *, Блог компании OTUSМашинное обучение *, Блог компании OTUS, Блог компании OTUS, Машинное обучение *, Машинное обучение *, *, Блог компании OTUS, Машинное обучение</t>
+  </si>
+  <si>
+    <t>Теги:mlмашинное обучениевалидация данныхобучение моделигиперпараметры, ml, машинное обучение, валидация данных, обучение модели, гиперпараметры</t>
+  </si>
+  <si>
+    <t>Gonkey, асинхронная коммуникация и новые мапы. Материалы с Golang Meetup</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/907294/</t>
+  </si>
+  <si>
+    <t>saigina_m</t>
+  </si>
+  <si>
+    <t>2025-05-06T13:04:16.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании Lamoda TechGo *, Блог компании Lamoda TechGo *, Блог компании Lamoda Tech, Блог компании Lamoda Tech, Go *, Go *, *, Блог компании Lamoda Tech, Go</t>
+  </si>
+  <si>
+    <t>Репортаж, Теги:митапымитапgolanggo, митапы, митап, golang, go</t>
+  </si>
+  <si>
     <t>Еще раз про Di-контейнеры в golang</t>
   </si>
   <si>
@@ -1152,19 +1209,49 @@
     <t>Теги:внедрение зависимостейархитектураgolangрефакторинг, внедрение зависимостей, архитектура, golang, рефакторинг</t>
   </si>
   <si>
-    <t>fit() для новичков</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/905858/</t>
-  </si>
-  <si>
-    <t>2025-05-16T12:05:01.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании OTUSМашинное обучение *, Блог компании OTUSМашинное обучение *, Блог компании OTUS, Блог компании OTUS, Машинное обучение *, Машинное обучение *, *, Блог компании OTUS, Машинное обучение</t>
-  </si>
-  <si>
-    <t>Теги:mlмашинное обучениевалидация данныхобучение моделигиперпараметры, ml, машинное обучение, валидация данных, обучение модели, гиперпараметры</t>
+    <t>Когортный анализ, LTV и RFM в SQL: коротко для новичков</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/901114/</t>
+  </si>
+  <si>
+    <t>2025-04-16T09:44:31.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании OTUSSQL * Анализ и проектирование систем *, Блог компании OTUSSQL * Анализ и проектирование систем *, Блог компании OTUS, Блог компании OTUS, SQL *, SQL *, *, Анализ и проектирование систем *, Анализ и проектирование систем *, *, Блог компании OTUS, SQL, Анализ и проектирование систем</t>
+  </si>
+  <si>
+    <t>Теги:sqlанализкогортный анализсистемный аналитикrfm сегментация, sql, анализ, когортный анализ, системный аналитик, rfm сегментация</t>
+  </si>
+  <si>
+    <t>Golang: почему select {} без default может убить ваше приложение</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/904740/</t>
+  </si>
+  <si>
+    <t>2025-04-29T05:39:16.000Z</t>
+  </si>
+  <si>
+    <t>Теги:golangGolang selectgoблокировка горутинпроизводительность Goзакрытие каналовdefault, golang, Golang select, go, блокировка горутин, производительность Go, закрытие каналов, default</t>
+  </si>
+  <si>
+    <t>Сборка на CMake для новичка</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/904992/</t>
+  </si>
+  <si>
+    <t>RdtyWorld</t>
+  </si>
+  <si>
+    <t>2025-04-28T06:16:10.000Z</t>
+  </si>
+  <si>
+    <t>C * C++ * Программирование *, C * C++ * Программирование *, C *, C *, *, C++ *, C++ *, *, Программирование *, Программирование *, *, C, C++, Программирование</t>
+  </si>
+  <si>
+    <t>Теги:cmakecmake инструкцияновичкамсборка проектасборка из исходников, cmake, cmake инструкция, новичкам, сборка проекта, сборка из исходников</t>
   </si>
   <si>
     <t>Golang Top 15 ошибок</t>
@@ -1203,90 +1290,96 @@
     <t>Теги:gooop, go, oop</t>
   </si>
   <si>
-    <t>Сборка на CMake для новичка</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/904992/</t>
-  </si>
-  <si>
-    <t>RdtyWorld</t>
-  </si>
-  <si>
-    <t>2025-04-28T06:16:10.000Z</t>
-  </si>
-  <si>
-    <t>C * C++ * Программирование *, C * C++ * Программирование *, C *, C *, *, C++ *, C++ *, *, Программирование *, Программирование *, *, C, C++, Программирование</t>
-  </si>
-  <si>
-    <t>Теги:cmakecmake инструкцияновичкамсборка проектасборка из исходников, cmake, cmake инструкция, новичкам, сборка проекта, сборка из исходников</t>
-  </si>
-  <si>
-    <t>Первый http сервер на С++, заметки для новичков</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/910222/</t>
-  </si>
-  <si>
-    <t>kkmspb</t>
-  </si>
-  <si>
-    <t>2025-05-17T16:59:47.000Z</t>
-  </si>
-  <si>
-    <t>PHP * JavaScript * C++ * Qt *, PHP * JavaScript * C++ * Qt *, PHP *, PHP *, *, JavaScript *, JavaScript *, *, C++ *, C++ *, *, Qt *, Qt *, *, PHP, JavaScript, C++, Qt</t>
-  </si>
-  <si>
-    <t>Теги:Content-Typeurlencodejsonbase64hex, Content-Type, urlencode, json, base64, hex</t>
-  </si>
-  <si>
-    <t>Golang: почему select {} без default может убить ваше приложение</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/904740/</t>
-  </si>
-  <si>
-    <t>2025-04-29T05:39:16.000Z</t>
-  </si>
-  <si>
-    <t>Теги:golangGolang selectgoблокировка горутинпроизводительность Goзакрытие каналовdefault, golang, Golang select, go, блокировка горутин, производительность Go, закрытие каналов, default</t>
-  </si>
-  <si>
-    <t>Gonkey, асинхронная коммуникация и новые мапы. Материалы с Golang Meetup</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/907294/</t>
-  </si>
-  <si>
-    <t>saigina_m</t>
-  </si>
-  <si>
-    <t>2025-05-06T13:04:16.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании Lamoda TechGo *, Блог компании Lamoda TechGo *, Блог компании Lamoda Tech, Блог компании Lamoda Tech, Go *, Go *, *, Блог компании Lamoda Tech, Go</t>
-  </si>
-  <si>
-    <t>Репортаж, Теги:митапымитапgolanggo, митапы, митап, golang, go</t>
-  </si>
-  <si>
-    <t>Когортный анализ, LTV и RFM в SQL: коротко для новичков</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/901114/</t>
-  </si>
-  <si>
-    <t>2025-04-16T09:44:31.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании OTUSSQL * Анализ и проектирование систем *, Блог компании OTUSSQL * Анализ и проектирование систем *, Блог компании OTUS, Блог компании OTUS, SQL *, SQL *, *, Анализ и проектирование систем *, Анализ и проектирование систем *, *, Блог компании OTUS, SQL, Анализ и проектирование систем</t>
-  </si>
-  <si>
-    <t>Теги:sqlанализкогортный анализсистемный аналитикrfm сегментация, sql, анализ, когортный анализ, системный аналитик, rfm сегментация</t>
-  </si>
-  <si>
     <t>мобильные приложения</t>
   </si>
   <si>
+    <t>Offline First в мобильных приложениях. Кэширование</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902060/</t>
+  </si>
+  <si>
+    <t>Friflex_dev</t>
+  </si>
+  <si>
+    <t>2025-04-18T09:12:10.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании FriflexРазработка мобильных приложений * Flutter * SQLite * SQL *, Блог компании FriflexРазработка мобильных приложений * Flutter * SQLite * SQL *, Блог компании Friflex, Блог компании Friflex, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Flutter *, Flutter *, *, SQLite *, SQLite *, *, SQL *, SQL *, *, Блог компании Friflex, Разработка мобильных приложений, Flutter, SQLite, SQL</t>
+  </si>
+  <si>
+    <t>Теги:offline firstкэширование, offline first, кэширование</t>
+  </si>
+  <si>
+    <t>Rafinad: сахар для UI-тестирования iOS-приложений</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/910380/</t>
+  </si>
+  <si>
+    <t>almazrafi</t>
+  </si>
+  <si>
+    <t>2025-05-26T08:35:00.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании hh.ruSwift * iOS * Разработка мобильных приложений * Тестирование мобильных приложений *, Блог компании hh.ruSwift * iOS * Разработка мобильных приложений * Тестирование мобильных приложений *, Блог компании hh.ru, Блог компании hh.ru, Swift *, Swift *, *, iOS *, iOS *, *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Тестирование мобильных приложений *, Тестирование мобильных приложений *, *, Блог компании hh.ru, Swift, iOS, Разработка мобильных приложений, Тестирование мобильных приложений</t>
+  </si>
+  <si>
+    <t>Теги:iosui-тестыui-тестированиетестированиеswiftswiftuiuikitxctestxcuitestdsl, ios, ui-тесты, ui-тестирование, тестирование, swift, swiftui, uikit, xctest, xcuitest, dsl</t>
+  </si>
+  <si>
+    <t>Content Based Theme в Android приложении</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/904258/</t>
+  </si>
+  <si>
+    <t>Dertefter</t>
+  </si>
+  <si>
+    <t>2025-04-25T05:35:13.000Z</t>
+  </si>
+  <si>
+    <t>Android * Дизайн мобильных приложений * Kotlin *, Android * Дизайн мобильных приложений * Kotlin *, Android *, Android *, *, Дизайн мобильных приложений *, Дизайн мобильных приложений *, *, Kotlin *, Kotlin *, *, Android, Дизайн мобильных приложений, Kotlin</t>
+  </si>
+  <si>
+    <t>Теги:material youkotlinandroid, material you, kotlin, android</t>
+  </si>
+  <si>
+    <t>Росреестр запустил мобильное приложение для граждан и кадастровых инженеров</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/904164/</t>
+  </si>
+  <si>
+    <t>AnnieBronson</t>
+  </si>
+  <si>
+    <t>2025-04-24T16:25:43.000Z</t>
+  </si>
+  <si>
+    <t>Разработка мобильных приложений * Android * Геоинформационные сервисы *, Разработка мобильных приложений * Android * Геоинформационные сервисы *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Android *, Android *, *, Геоинформационные сервисы *, Геоинформационные сервисы *, *, Разработка мобильных приложений, Android, Геоинформационные сервисы</t>
+  </si>
+  <si>
+    <t>Теги:росреестркадастркадастровые картынедвижимостьмобильные приложения, росреестр, кадастр, кадастровые карты, недвижимость, мобильные приложения</t>
+  </si>
+  <si>
+    <t>Offline First в мобильных приложениях. CRUD на стороне клиента</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/904448/</t>
+  </si>
+  <si>
+    <t>2025-04-25T12:07:36.000Z</t>
+  </si>
+  <si>
+    <t>Блог компании FriflexРазработка мобильных приложений * SQL * NoSQL *, Блог компании FriflexРазработка мобильных приложений * SQL * NoSQL *, Блог компании Friflex, Блог компании Friflex, Разработка мобильных приложений *, Разработка мобильных приложений *, *, SQL *, SQL *, *, NoSQL *, NoSQL *, *, Блог компании Friflex, Разработка мобильных приложений, SQL, NoSQL</t>
+  </si>
+  <si>
+    <t>Теги:offline-firstoffline web applicationsразработка мобильных приложений, offline-first, offline web applications, разработка мобильных приложений</t>
+  </si>
+  <si>
     <t>Весеннее приложение для Android</t>
   </si>
   <si>
@@ -1305,6 +1398,42 @@
     <t>Теги:приложения для android, приложения для android</t>
   </si>
   <si>
+    <t>Как мобильное приложение для ВодоходЪ вырастило средний чек на 15%</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/901390/</t>
+  </si>
+  <si>
+    <t>delaweb</t>
+  </si>
+  <si>
+    <t>2025-04-16T12:38:41.000Z</t>
+  </si>
+  <si>
+    <t>Node.JS * PostgreSQL * Nginx * Веб-разработка * Разработка мобильных приложений *, Node.JS * PostgreSQL * Nginx * Веб-разработка * Разработка мобильных приложений *, Node.JS *, Node.JS *, *, PostgreSQL *, PostgreSQL *, *, Nginx *, Nginx *, *, Веб-разработка *, Веб-разработка *, *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Node.JS, PostgreSQL, Nginx, Веб-разработка, Разработка мобильных приложений</t>
+  </si>
+  <si>
+    <t>Теги:разработкаразработка сайтовразработка поразработка под androidразработка под iosразработка мобильных приложений, разработка, разработка сайтов, разработка по, разработка под android, разработка под ios, разработка мобильных приложений</t>
+  </si>
+  <si>
+    <t>Google выпустил приложение NotebookLM для Android и iOS</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/910936/</t>
+  </si>
+  <si>
+    <t>maybe_elf</t>
+  </si>
+  <si>
+    <t>2025-05-20T06:37:19.000Z</t>
+  </si>
+  <si>
+    <t>Android * iOS * Разработка мобильных приложений * Искусственный интеллект, Android * iOS * Разработка мобильных приложений * Искусственный интеллект, Android *, Android *, *, iOS *, iOS *, *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Искусственный интеллект, Искусственный интеллект, Android, iOS, Разработка мобильных приложений, Искусственный интеллект</t>
+  </si>
+  <si>
+    <t>Теги:googlenotebooklmприложение для androidприложение для iosискусственный интеллектблокнотподкасты, google, notebooklm, приложение для android, приложение для ios, искусственный интеллект, блокнот, подкасты</t>
+  </si>
+  <si>
     <t>Raycast выпустила приложение для iOS</t>
   </si>
   <si>
@@ -1320,78 +1449,6 @@
     <t>Теги:Raycastiosприложениеiphoneискусственный интеллектмашинное обучениенейросети, Raycast, ios, приложение, iphone, искусственный интеллект, машинное обучение, нейросети</t>
   </si>
   <si>
-    <t>Google выпустил приложение NotebookLM для Android и iOS</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/910936/</t>
-  </si>
-  <si>
-    <t>maybe_elf</t>
-  </si>
-  <si>
-    <t>2025-05-20T06:37:19.000Z</t>
-  </si>
-  <si>
-    <t>Android * iOS * Разработка мобильных приложений * Искусственный интеллект, Android * iOS * Разработка мобильных приложений * Искусственный интеллект, Android *, Android *, *, iOS *, iOS *, *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Искусственный интеллект, Искусственный интеллект, Android, iOS, Разработка мобильных приложений, Искусственный интеллект</t>
-  </si>
-  <si>
-    <t>Теги:googlenotebooklmприложение для androidприложение для iosискусственный интеллектблокнотподкасты, google, notebooklm, приложение для android, приложение для ios, искусственный интеллект, блокнот, подкасты</t>
-  </si>
-  <si>
-    <t>Offline First в мобильных приложениях. Кэширование</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902060/</t>
-  </si>
-  <si>
-    <t>Friflex_dev</t>
-  </si>
-  <si>
-    <t>2025-04-18T09:12:10.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании FriflexРазработка мобильных приложений * Flutter * SQLite * SQL *, Блог компании FriflexРазработка мобильных приложений * Flutter * SQLite * SQL *, Блог компании Friflex, Блог компании Friflex, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Flutter *, Flutter *, *, SQLite *, SQLite *, *, SQL *, SQL *, *, Блог компании Friflex, Разработка мобильных приложений, Flutter, SQLite, SQL</t>
-  </si>
-  <si>
-    <t>Теги:offline firstкэширование, offline first, кэширование</t>
-  </si>
-  <si>
-    <t>Content Based Theme в Android приложении</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/904258/</t>
-  </si>
-  <si>
-    <t>Dertefter</t>
-  </si>
-  <si>
-    <t>2025-04-25T05:35:13.000Z</t>
-  </si>
-  <si>
-    <t>Android * Дизайн мобильных приложений * Kotlin *, Android * Дизайн мобильных приложений * Kotlin *, Android *, Android *, *, Дизайн мобильных приложений *, Дизайн мобильных приложений *, *, Kotlin *, Kotlin *, *, Android, Дизайн мобильных приложений, Kotlin</t>
-  </si>
-  <si>
-    <t>Теги:material youkotlinandroid, material you, kotlin, android</t>
-  </si>
-  <si>
-    <t>Rafinad: сахар для UI-тестирования iOS-приложений</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/910380/</t>
-  </si>
-  <si>
-    <t>almazrafi</t>
-  </si>
-  <si>
-    <t>2025-05-26T08:35:00.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании hh.ruSwift * iOS * Разработка мобильных приложений * Тестирование мобильных приложений *, Блог компании hh.ruSwift * iOS * Разработка мобильных приложений * Тестирование мобильных приложений *, Блог компании hh.ru, Блог компании hh.ru, Swift *, Swift *, *, iOS *, iOS *, *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Тестирование мобильных приложений *, Тестирование мобильных приложений *, *, Блог компании hh.ru, Swift, iOS, Разработка мобильных приложений, Тестирование мобильных приложений</t>
-  </si>
-  <si>
-    <t>Теги:iosui-тестыui-тестированиетестированиеswiftswiftuiuikitxctestxcuitestdsl, ios, ui-тесты, ui-тестирование, тестирование, swift, swiftui, uikit, xctest, xcuitest, dsl</t>
-  </si>
-  <si>
     <t>Приложение Move to iOS теперь может переносить историю вызовов и голосовые записи с Android</t>
   </si>
   <si>
@@ -1407,57 +1464,6 @@
     <t>Теги:move to iosappleandroidперенос данныхмобильные приложениясмартфоныобновлениеголосовые записи, move to ios, apple, android, перенос данных, мобильные приложения, смартфоны, обновление, голосовые записи</t>
   </si>
   <si>
-    <t>Как мобильное приложение для ВодоходЪ вырастило средний чек на 15%</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/901390/</t>
-  </si>
-  <si>
-    <t>delaweb</t>
-  </si>
-  <si>
-    <t>2025-04-16T12:38:41.000Z</t>
-  </si>
-  <si>
-    <t>Node.JS * PostgreSQL * Nginx * Веб-разработка * Разработка мобильных приложений *, Node.JS * PostgreSQL * Nginx * Веб-разработка * Разработка мобильных приложений *, Node.JS *, Node.JS *, *, PostgreSQL *, PostgreSQL *, *, Nginx *, Nginx *, *, Веб-разработка *, Веб-разработка *, *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Node.JS, PostgreSQL, Nginx, Веб-разработка, Разработка мобильных приложений</t>
-  </si>
-  <si>
-    <t>Теги:разработкаразработка сайтовразработка поразработка под androidразработка под iosразработка мобильных приложений, разработка, разработка сайтов, разработка по, разработка под android, разработка под ios, разработка мобильных приложений</t>
-  </si>
-  <si>
-    <t>Росреестр запустил мобильное приложение для граждан и кадастровых инженеров</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/904164/</t>
-  </si>
-  <si>
-    <t>AnnieBronson</t>
-  </si>
-  <si>
-    <t>2025-04-24T16:25:43.000Z</t>
-  </si>
-  <si>
-    <t>Разработка мобильных приложений * Android * Геоинформационные сервисы *, Разработка мобильных приложений * Android * Геоинформационные сервисы *, Разработка мобильных приложений *, Разработка мобильных приложений *, *, Android *, Android *, *, Геоинформационные сервисы *, Геоинформационные сервисы *, *, Разработка мобильных приложений, Android, Геоинформационные сервисы</t>
-  </si>
-  <si>
-    <t>Теги:росреестркадастркадастровые картынедвижимостьмобильные приложения, росреестр, кадастр, кадастровые карты, недвижимость, мобильные приложения</t>
-  </si>
-  <si>
-    <t>Offline First в мобильных приложениях. CRUD на стороне клиента</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/904448/</t>
-  </si>
-  <si>
-    <t>2025-04-25T12:07:36.000Z</t>
-  </si>
-  <si>
-    <t>Блог компании FriflexРазработка мобильных приложений * SQL * NoSQL *, Блог компании FriflexРазработка мобильных приложений * SQL * NoSQL *, Блог компании Friflex, Блог компании Friflex, Разработка мобильных приложений *, Разработка мобильных приложений *, *, SQL *, SQL *, *, NoSQL *, NoSQL *, *, Блог компании Friflex, Разработка мобильных приложений, SQL, NoSQL</t>
-  </si>
-  <si>
-    <t>Теги:offline-firstoffline web applicationsразработка мобильных приложений, offline-first, offline web applications, разработка мобильных приложений</t>
-  </si>
-  <si>
     <t>разработка игр unity</t>
   </si>
   <si>
@@ -1497,6 +1503,63 @@
     <t>Теги:разработка игрмаркетинг игригрымонетизация игригровая индустрияигры в бизнесе, разработка игр, маркетинг игр, игры, монетизация игр, игровая индустрия, игры в бизнесе</t>
   </si>
   <si>
+    <t>Pac-Man в визуальной новелле: зачем мы добавили мини-игру, и как это работает</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/906118/</t>
+  </si>
+  <si>
+    <t>Sombergames</t>
+  </si>
+  <si>
+    <t>2025-04-30T18:35:36.000Z</t>
+  </si>
+  <si>
+    <t>Unity * Разработка игр *, Unity * Разработка игр *, Unity *, Unity *, *, Разработка игр *, Разработка игр *, *, Unity, Разработка игр</t>
+  </si>
+  <si>
+    <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новеллахоррор игрыиндиразработка игринди-разработкаигровые автоматы, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, хоррор игры, инди, разработка игр, инди-разработка, игровые автоматы</t>
+  </si>
+  <si>
+    <t>От первых штрихов до 2D анимации прямо в Unity</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/904644/</t>
+  </si>
+  <si>
+    <t>2025-04-26T11:55:59.000Z</t>
+  </si>
+  <si>
+    <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новелларазработка игринди-разработкаиндианимация2d-графика, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, разработка игр, инди-разработка, инди, анимация, 2d-графика</t>
+  </si>
+  <si>
+    <t>Как любовь к играм и американским хоррорам привела к созданию «Pink Noise»</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/902590/</t>
+  </si>
+  <si>
+    <t>2025-04-20T20:15:32.000Z</t>
+  </si>
+  <si>
+    <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новелларазработка игрхоррор игрыхорроринди-разработкаинди, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, разработка игр, хоррор игры, хоррор, инди-разработка, инди</t>
+  </si>
+  <si>
+    <t>Движок Unity 6 в Китае заменят проектом Tuanjie</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/901956/</t>
+  </si>
+  <si>
+    <t>2025-04-18T06:07:28.000Z</t>
+  </si>
+  <si>
+    <t>Игры и игровые консолиРазработка игр * Unity *, Игры и игровые консолиРазработка игр * Unity *, Игры и игровые консоли, Игры и игровые консоли, Разработка игр *, Разработка игр *, *, Unity *, Unity *, *, Игры и игровые консоли, Разработка игр, Unity</t>
+  </si>
+  <si>
+    <t>Теги:unityигровой движоккитайразработка игрразработчики игрлокализация продуктов, unity, игровой движок, китай, разработка игр, разработчики игр, локализация продуктов</t>
+  </si>
+  <si>
     <t>SWE-Agent: как AI-ассистенты меняют правила игры в разработке</t>
   </si>
   <si>
@@ -1533,48 +1596,6 @@
     <t>Репортаж, Теги:мероприятие для разработчиковвшб ниу вшэрелизы, мероприятие для разработчиков, вшб ниу вшэ, релизы</t>
   </si>
   <si>
-    <t>Как любовь к играм и американским хоррорам привела к созданию «Pink Noise»</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/902590/</t>
-  </si>
-  <si>
-    <t>Sombergames</t>
-  </si>
-  <si>
-    <t>2025-04-20T20:15:32.000Z</t>
-  </si>
-  <si>
-    <t>Unity * Разработка игр *, Unity * Разработка игр *, Unity *, Unity *, *, Разработка игр *, Разработка игр *, *, Unity, Разработка игр</t>
-  </si>
-  <si>
-    <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новелларазработка игрхоррор игрыхорроринди-разработкаинди, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, разработка игр, хоррор игры, хоррор, инди-разработка, инди</t>
-  </si>
-  <si>
-    <t>От первых штрихов до 2D анимации прямо в Unity</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/904644/</t>
-  </si>
-  <si>
-    <t>2025-04-26T11:55:59.000Z</t>
-  </si>
-  <si>
-    <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новелларазработка игринди-разработкаиндианимация2d-графика, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, разработка игр, инди-разработка, инди, анимация, 2d-графика</t>
-  </si>
-  <si>
-    <t>Pac-Man в визуальной новелле: зачем мы добавили мини-игру, и как это работает</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/906118/</t>
-  </si>
-  <si>
-    <t>2025-04-30T18:35:36.000Z</t>
-  </si>
-  <si>
-    <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новеллахоррор игрыиндиразработка игринди-разработкаигровые автоматы, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, хоррор игры, инди, разработка игр, инди-разработка, игровые автоматы</t>
-  </si>
-  <si>
     <t>А точно ли самый простой жанр?</t>
   </si>
   <si>
@@ -1585,21 +1606,6 @@
   </si>
   <si>
     <t>Теги:gamedevindiegamegamedevelopmentgamestudiesвизуальная новеллахоррор игрыиндиразработка игринди-разработка, gamedev, indiegame, gamedevelopment, gamestudies, визуальная новелла, хоррор игры, инди, разработка игр, инди-разработка</t>
-  </si>
-  <si>
-    <t>Движок Unity 6 в Китае заменят проектом Tuanjie</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/901956/</t>
-  </si>
-  <si>
-    <t>2025-04-18T06:07:28.000Z</t>
-  </si>
-  <si>
-    <t>Игры и игровые консолиРазработка игр * Unity *, Игры и игровые консолиРазработка игр * Unity *, Игры и игровые консоли, Игры и игровые консоли, Разработка игр *, Разработка игр *, *, Unity *, Unity *, *, Игры и игровые консоли, Разработка игр, Unity</t>
-  </si>
-  <si>
-    <t>Теги:unityигровой движоккитайразработка игрразработчики игрлокализация продуктов, unity, игровой движок, китай, разработка игр, разработчики игр, локализация продуктов</t>
   </si>
 </sst>
 </file>
@@ -1962,14 +1968,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="33.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="108" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="108" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2006,8 +2013,14 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2015,10 +2028,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2026,11 +2039,11 @@
       <c r="F2">
         <v>246.63338999999999</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="G2">
+        <v>0.99999996269153624</v>
+      </c>
+      <c r="H2">
+        <v>0.99999997388407524</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -2044,31 +2057,37 @@
       <c r="L2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>237.08142000000001</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
+        <v>209.10290000000001</v>
+      </c>
+      <c r="G3">
+        <v>0.99999983457653463</v>
+      </c>
+      <c r="H3">
+        <v>0.99999988420357422</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -2082,8 +2101,14 @@
       <c r="L3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2091,22 +2116,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>224.43588</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
+        <v>209.10290000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.99999968631485658</v>
+      </c>
+      <c r="H4">
+        <v>0.9999997804203995</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -2115,51 +2140,63 @@
         <v>29</v>
       </c>
       <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
         <v>30</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>224.43588</v>
-      </c>
-      <c r="G5" t="s">
+        <v>209.10290000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.99999966704268306</v>
+      </c>
+      <c r="H5">
+        <v>0.99999976692987813</v>
+      </c>
+      <c r="I5" t="s">
         <v>32</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>33</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>35</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>36</v>
       </c>
-      <c r="L5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -2167,37 +2204,43 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>220.03755000000001</v>
-      </c>
-      <c r="G6" t="s">
+        <v>237.08142000000001</v>
+      </c>
+      <c r="G6">
+        <v>0.99999949796215692</v>
+      </c>
+      <c r="H6">
+        <v>0.99999964857350987</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
         <v>38</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>39</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>40</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>41</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
         <v>42</v>
       </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2205,124 +2248,142 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>209.10290000000001</v>
-      </c>
-      <c r="G7" t="s">
+        <v>224.43588</v>
+      </c>
+      <c r="G7">
+        <v>0.99999804614322008</v>
+      </c>
+      <c r="H7">
+        <v>0.9999986323002541</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" t="s">
         <v>44</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>46</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>47</v>
       </c>
-      <c r="K7" t="s">
+      <c r="N7" t="s">
         <v>48</v>
       </c>
-      <c r="L7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>209.10290000000001</v>
-      </c>
-      <c r="G8" t="s">
+        <v>220.03755000000001</v>
+      </c>
+      <c r="G8">
+        <v>0.99999795943235126</v>
+      </c>
+      <c r="H8">
+        <v>0.99999857160264582</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
         <v>50</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>51</v>
       </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>52</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>53</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9">
-        <v>209.10290000000001</v>
-      </c>
-      <c r="G9" t="s">
+        <v>224.43588</v>
+      </c>
+      <c r="G9">
+        <v>0.99999658564176241</v>
+      </c>
+      <c r="H9">
+        <v>0.99999760994923359</v>
+      </c>
+      <c r="I9" t="s">
         <v>55</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>56</v>
       </c>
-      <c r="I9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>57</v>
-      </c>
-      <c r="K9" t="s">
-        <v>48</v>
       </c>
       <c r="L9" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2330,11 +2391,11 @@
       <c r="F10">
         <v>209.10290000000001</v>
       </c>
-      <c r="G10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" t="s">
-        <v>60</v>
+      <c r="G10">
+        <v>0.99999450379672916</v>
+      </c>
+      <c r="H10">
+        <v>0.99999615265771036</v>
       </c>
       <c r="I10" t="s">
         <v>61</v>
@@ -2348,19 +2409,25 @@
       <c r="L10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -2368,11 +2435,11 @@
       <c r="F11">
         <v>209.10290000000001</v>
       </c>
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
+      <c r="G11">
+        <v>0.99998611583719743</v>
+      </c>
+      <c r="H11">
+        <v>0.99999028108603816</v>
       </c>
       <c r="I11" t="s">
         <v>67</v>
@@ -2386,31 +2453,37 @@
       <c r="L11" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" t="s">
+        <v>71</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>40.274284000000002</v>
-      </c>
-      <c r="G12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" t="s">
-        <v>73</v>
+        <v>37.073610000000002</v>
+      </c>
+      <c r="G12">
+        <v>0.96937727020666076</v>
+      </c>
+      <c r="H12">
+        <v>0.78978491914466253</v>
       </c>
       <c r="I12" t="s">
         <v>74</v>
@@ -2424,8 +2497,14 @@
       <c r="L12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0</v>
       </c>
@@ -2433,10 +2512,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2444,11 +2523,11 @@
       <c r="F13">
         <v>39.301926000000002</v>
       </c>
-      <c r="G13" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" t="s">
-        <v>79</v>
+      <c r="G13">
+        <v>0.93872923429750432</v>
+      </c>
+      <c r="H13">
+        <v>0.77501624200825303</v>
       </c>
       <c r="I13" t="s">
         <v>80</v>
@@ -2457,51 +2536,63 @@
         <v>81</v>
       </c>
       <c r="K13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13" t="s">
         <v>82</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>38.772635999999999</v>
-      </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
+        <v>35.084408000000003</v>
+      </c>
+      <c r="G14">
+        <v>0.94064626676022167</v>
+      </c>
+      <c r="H14">
+        <v>0.76370561073215515</v>
+      </c>
+      <c r="I14" t="s">
         <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>74</v>
       </c>
       <c r="J14" t="s">
         <v>86</v>
       </c>
       <c r="K14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" t="s">
         <v>87</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -2509,75 +2600,87 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15">
-        <v>37.073610000000002</v>
-      </c>
-      <c r="G15" t="s">
+        <v>40.274284000000002</v>
+      </c>
+      <c r="G15">
+        <v>0.90848353077856681</v>
+      </c>
+      <c r="H15">
+        <v>0.7567613235449967</v>
+      </c>
+      <c r="I15" t="s">
         <v>89</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>90</v>
       </c>
-      <c r="I15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>91</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>92</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
       <c r="F16">
-        <v>35.084408000000003</v>
-      </c>
-      <c r="G16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" t="s">
+        <v>30.195633000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.87014368610962611</v>
+      </c>
+      <c r="H16">
+        <v>0.69968747927673824</v>
+      </c>
+      <c r="I16" t="s">
         <v>95</v>
-      </c>
-      <c r="I16" t="s">
-        <v>80</v>
       </c>
       <c r="J16" t="s">
         <v>96</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="L16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="M16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -2585,37 +2688,43 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17">
         <v>6</v>
       </c>
       <c r="F17">
-        <v>33.249862999999998</v>
-      </c>
-      <c r="G17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" t="s">
-        <v>99</v>
+        <v>29.479500000000002</v>
+      </c>
+      <c r="G17">
+        <v>0.86249783687622428</v>
+      </c>
+      <c r="H17">
+        <v>0.69218698581335691</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="M17" t="s">
+        <v>105</v>
+      </c>
+      <c r="N17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -2623,10 +2732,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2634,26 +2743,32 @@
       <c r="F18">
         <v>33.249862999999998</v>
       </c>
-      <c r="G18" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" t="s">
-        <v>105</v>
+      <c r="G18">
+        <v>0.8281542067625749</v>
+      </c>
+      <c r="H18">
+        <v>0.67945753373380235</v>
       </c>
       <c r="I18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="M18" t="s">
+        <v>111</v>
+      </c>
+      <c r="N18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2661,37 +2776,43 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>8</v>
       </c>
       <c r="F19">
-        <v>30.195633000000001</v>
-      </c>
-      <c r="G19" t="s">
-        <v>110</v>
-      </c>
-      <c r="H19" t="s">
-        <v>111</v>
+        <v>33.249862999999998</v>
+      </c>
+      <c r="G19">
+        <v>0.82445743307820185</v>
+      </c>
+      <c r="H19">
+        <v>0.67686979215474119</v>
       </c>
       <c r="I19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="M19" t="s">
+        <v>117</v>
+      </c>
+      <c r="N19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2699,37 +2820,43 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
       <c r="F20">
-        <v>29.479500000000002</v>
-      </c>
-      <c r="G20" t="s">
-        <v>116</v>
-      </c>
-      <c r="H20" t="s">
-        <v>117</v>
+        <v>38.772635999999999</v>
+      </c>
+      <c r="G20">
+        <v>0.49780257338076811</v>
+      </c>
+      <c r="H20">
+        <v>0.46477970936653762</v>
       </c>
       <c r="I20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K20" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="L20" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20" t="s">
+        <v>122</v>
+      </c>
+      <c r="N20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -2737,10 +2864,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -2748,11 +2875,11 @@
       <c r="F21">
         <v>29.479500000000002</v>
       </c>
-      <c r="G21" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21" t="s">
-        <v>123</v>
+      <c r="G21">
+        <v>0.44156931165814711</v>
+      </c>
+      <c r="H21">
+        <v>0.39753701816070303</v>
       </c>
       <c r="I21" t="s">
         <v>124</v>
@@ -2766,8 +2893,14 @@
       <c r="L21" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>128</v>
+      </c>
+      <c r="N21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2775,10 +2908,10 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2786,11 +2919,11 @@
       <c r="F22">
         <v>246.63338999999999</v>
       </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
+      <c r="G22">
+        <v>0.99999997395938434</v>
+      </c>
+      <c r="H22">
+        <v>0.99999998177156901</v>
       </c>
       <c r="I22" t="s">
         <v>16</v>
@@ -2804,8 +2937,14 @@
       <c r="L22" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
@@ -2813,22 +2952,22 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>237.08142000000001</v>
-      </c>
-      <c r="G23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" t="s">
-        <v>21</v>
+        <v>209.10290000000001</v>
+      </c>
+      <c r="G23">
+        <v>0.99999987923737022</v>
+      </c>
+      <c r="H23">
+        <v>0.99999991546615918</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -2842,8 +2981,14 @@
       <c r="L23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
@@ -2851,37 +2996,43 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24">
-        <v>224.43588</v>
-      </c>
-      <c r="G24" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" t="s">
-        <v>27</v>
+        <v>209.10290000000001</v>
+      </c>
+      <c r="G24">
+        <v>0.99999977246483485</v>
+      </c>
+      <c r="H24">
+        <v>0.99999984072538428</v>
       </c>
       <c r="I24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K24" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="M24" t="s">
+        <v>35</v>
+      </c>
+      <c r="N24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1</v>
       </c>
@@ -2889,37 +3040,43 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25">
-        <v>224.43588</v>
-      </c>
-      <c r="G25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" t="s">
-        <v>33</v>
+        <v>209.10290000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.99999976384739964</v>
+      </c>
+      <c r="H25">
+        <v>0.99999983469317977</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J25" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K25" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="M25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -2927,113 +3084,131 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26">
-        <v>220.03755000000001</v>
-      </c>
-      <c r="G26" t="s">
+        <v>237.08142000000001</v>
+      </c>
+      <c r="G26">
+        <v>0.99999961067733778</v>
+      </c>
+      <c r="H26">
+        <v>0.99999972747413635</v>
+      </c>
+      <c r="I26" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" t="s">
         <v>38</v>
       </c>
-      <c r="H26" t="s">
+      <c r="K26" t="s">
         <v>39</v>
       </c>
-      <c r="I26" t="s">
+      <c r="L26" t="s">
         <v>40</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>41</v>
       </c>
-      <c r="K26" t="s">
+      <c r="N26" t="s">
         <v>42</v>
       </c>
-      <c r="L26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>6</v>
       </c>
       <c r="F27">
-        <v>209.10290000000001</v>
-      </c>
-      <c r="G27" t="s">
+        <v>224.43588</v>
+      </c>
+      <c r="G27">
+        <v>0.99999892281293634</v>
+      </c>
+      <c r="H27">
+        <v>0.99999924596905543</v>
+      </c>
+      <c r="I27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" t="s">
         <v>44</v>
       </c>
-      <c r="H27" t="s">
+      <c r="K27" t="s">
         <v>45</v>
       </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
         <v>46</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>47</v>
       </c>
-      <c r="K27" t="s">
+      <c r="N27" t="s">
         <v>48</v>
       </c>
-      <c r="L27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>7</v>
       </c>
       <c r="F28">
-        <v>209.10290000000001</v>
-      </c>
-      <c r="G28" t="s">
+        <v>220.03755000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.99999843517168396</v>
+      </c>
+      <c r="H28">
+        <v>0.99999890462017871</v>
+      </c>
+      <c r="I28" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" t="s">
         <v>50</v>
       </c>
-      <c r="H28" t="s">
+      <c r="K28" t="s">
         <v>51</v>
       </c>
-      <c r="I28" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>52</v>
       </c>
-      <c r="K28" t="s">
+      <c r="M28" t="s">
         <v>53</v>
       </c>
-      <c r="L28" t="s">
+      <c r="N28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1</v>
       </c>
@@ -3041,37 +3216,43 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29">
-        <v>209.10290000000001</v>
-      </c>
-      <c r="G29" t="s">
+        <v>224.43588</v>
+      </c>
+      <c r="G29">
+        <v>0.99999757455085359</v>
+      </c>
+      <c r="H29">
+        <v>0.99999830218559738</v>
+      </c>
+      <c r="I29" t="s">
         <v>55</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>56</v>
       </c>
-      <c r="I29" t="s">
-        <v>46</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>57</v>
-      </c>
-      <c r="K29" t="s">
-        <v>48</v>
       </c>
       <c r="L29" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -3079,10 +3260,10 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E30">
         <v>9</v>
@@ -3090,11 +3271,11 @@
       <c r="F30">
         <v>209.10290000000001</v>
       </c>
-      <c r="G30" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" t="s">
-        <v>60</v>
+      <c r="G30">
+        <v>0.9999957153480582</v>
+      </c>
+      <c r="H30">
+        <v>0.99999700074364073</v>
       </c>
       <c r="I30" t="s">
         <v>61</v>
@@ -3108,19 +3289,25 @@
       <c r="L30" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31">
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -3128,11 +3315,11 @@
       <c r="F31">
         <v>209.10290000000001</v>
       </c>
-      <c r="G31" t="s">
-        <v>65</v>
-      </c>
-      <c r="H31" t="s">
-        <v>66</v>
+      <c r="G31">
+        <v>0.99999286490854256</v>
+      </c>
+      <c r="H31">
+        <v>0.99999500543597963</v>
       </c>
       <c r="I31" t="s">
         <v>67</v>
@@ -3146,8 +3333,14 @@
       <c r="L31" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M31" t="s">
+        <v>71</v>
+      </c>
+      <c r="N31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1</v>
       </c>
@@ -3155,10 +3348,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -3166,11 +3359,11 @@
       <c r="F32">
         <v>66.244039999999998</v>
       </c>
-      <c r="G32" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" t="s">
-        <v>131</v>
+      <c r="G32">
+        <v>0.95132778806673168</v>
+      </c>
+      <c r="H32">
+        <v>0.86466157164671209</v>
       </c>
       <c r="I32" t="s">
         <v>132</v>
@@ -3184,8 +3377,14 @@
       <c r="L32" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>136</v>
+      </c>
+      <c r="N32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1</v>
       </c>
@@ -3193,22 +3392,22 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>66.244039999999998</v>
-      </c>
-      <c r="G33" t="s">
-        <v>136</v>
-      </c>
-      <c r="H33" t="s">
-        <v>137</v>
+        <v>62.869278000000001</v>
+      </c>
+      <c r="G33">
+        <v>0.9540197740583809</v>
+      </c>
+      <c r="H33">
+        <v>0.85642167584086659</v>
       </c>
       <c r="I33" t="s">
         <v>138</v>
@@ -3217,13 +3416,19 @@
         <v>139</v>
       </c>
       <c r="K33" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" t="s">
         <v>140</v>
       </c>
-      <c r="L33" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M33" t="s">
+        <v>136</v>
+      </c>
+      <c r="N33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -3231,60 +3436,66 @@
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34">
-        <v>62.869278000000001</v>
-      </c>
-      <c r="G34" t="s">
+        <v>59.824973999999997</v>
+      </c>
+      <c r="G34">
+        <v>0.88169363814223556</v>
+      </c>
+      <c r="H34">
+        <v>0.79666046869956486</v>
+      </c>
+      <c r="I34" t="s">
+        <v>141</v>
+      </c>
+      <c r="J34" t="s">
         <v>142</v>
       </c>
-      <c r="H34" t="s">
+      <c r="K34" t="s">
         <v>143</v>
       </c>
-      <c r="I34" t="s">
-        <v>138</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="L34" t="s">
         <v>144</v>
       </c>
-      <c r="K34" t="s">
-        <v>140</v>
-      </c>
-      <c r="L34" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" t="s">
+        <v>145</v>
+      </c>
+      <c r="N34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>4</v>
       </c>
       <c r="F35">
-        <v>61.308959999999999</v>
-      </c>
-      <c r="G35" t="s">
-        <v>145</v>
-      </c>
-      <c r="H35" t="s">
-        <v>146</v>
+        <v>56.641129999999997</v>
+      </c>
+      <c r="G35">
+        <v>0.83833611928148966</v>
+      </c>
+      <c r="H35">
+        <v>0.75675867349704273</v>
       </c>
       <c r="I35" t="s">
         <v>147</v>
@@ -3298,8 +3509,14 @@
       <c r="L35" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" t="s">
+        <v>151</v>
+      </c>
+      <c r="N35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1</v>
       </c>
@@ -3307,22 +3524,22 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>5</v>
       </c>
       <c r="F36">
-        <v>59.824973999999997</v>
-      </c>
-      <c r="G36" t="s">
-        <v>151</v>
-      </c>
-      <c r="H36" t="s">
-        <v>152</v>
+        <v>58.782775999999998</v>
+      </c>
+      <c r="G36">
+        <v>0.79408421147812136</v>
+      </c>
+      <c r="H36">
+        <v>0.73220727603468494</v>
       </c>
       <c r="I36" t="s">
         <v>153</v>
@@ -3336,31 +3553,37 @@
       <c r="L36" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" t="s">
+        <v>157</v>
+      </c>
+      <c r="N36" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E37">
         <v>6</v>
       </c>
       <c r="F37">
-        <v>58.782775999999998</v>
-      </c>
-      <c r="G37" t="s">
-        <v>157</v>
-      </c>
-      <c r="H37" t="s">
-        <v>158</v>
+        <v>66.244039999999998</v>
+      </c>
+      <c r="G37">
+        <v>0.75962179850927314</v>
+      </c>
+      <c r="H37">
+        <v>0.73046737895649116</v>
       </c>
       <c r="I37" t="s">
         <v>159</v>
@@ -3374,31 +3597,37 @@
       <c r="L37" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37" t="s">
+        <v>163</v>
+      </c>
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>7</v>
       </c>
       <c r="F38">
-        <v>56.641129999999997</v>
-      </c>
-      <c r="G38" t="s">
-        <v>163</v>
-      </c>
-      <c r="H38" t="s">
-        <v>164</v>
+        <v>61.308959999999999</v>
+      </c>
+      <c r="G38">
+        <v>0.60580442928683076</v>
+      </c>
+      <c r="H38">
+        <v>0.60798998050078146</v>
       </c>
       <c r="I38" t="s">
         <v>165</v>
@@ -3412,107 +3641,125 @@
       <c r="L38" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38" t="s">
+        <v>169</v>
+      </c>
+      <c r="N38" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E39">
         <v>8</v>
       </c>
       <c r="F39">
-        <v>52.874718000000001</v>
-      </c>
-      <c r="G39" t="s">
-        <v>169</v>
-      </c>
-      <c r="H39" t="s">
-        <v>170</v>
+        <v>31.935421000000002</v>
+      </c>
+      <c r="G39">
+        <v>0.56533325876141161</v>
+      </c>
+      <c r="H39">
+        <v>0.49153954413298812</v>
       </c>
       <c r="I39" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K39" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="M39" t="s">
+        <v>175</v>
+      </c>
+      <c r="N39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E40">
         <v>9</v>
       </c>
       <c r="F40">
-        <v>33.543194</v>
-      </c>
-      <c r="G40" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" t="s">
-        <v>174</v>
+        <v>52.874718000000001</v>
+      </c>
+      <c r="G40">
+        <v>0.39901116241391921</v>
+      </c>
+      <c r="H40">
+        <v>0.43793196768974341</v>
       </c>
       <c r="I40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K40" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="L40" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+      <c r="M40" t="s">
+        <v>53</v>
+      </c>
+      <c r="N40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E41">
         <v>10</v>
       </c>
       <c r="F41">
-        <v>31.935421000000002</v>
-      </c>
-      <c r="G41" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41" t="s">
-        <v>180</v>
+        <v>33.543194</v>
+      </c>
+      <c r="G41">
+        <v>0.37924029590657421</v>
+      </c>
+      <c r="H41">
+        <v>0.36609778913460189</v>
       </c>
       <c r="I41" t="s">
         <v>181</v>
@@ -3526,8 +3773,14 @@
       <c r="L41" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M41" t="s">
+        <v>185</v>
+      </c>
+      <c r="N41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0</v>
       </c>
@@ -3535,22 +3788,22 @@
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>142.86761000000001</v>
-      </c>
-      <c r="G42" t="s">
-        <v>186</v>
-      </c>
-      <c r="H42" t="s">
-        <v>187</v>
+        <v>141.02930000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.99993822823129608</v>
+      </c>
+      <c r="H42">
+        <v>0.99995675976190723</v>
       </c>
       <c r="I42" t="s">
         <v>188</v>
@@ -3564,8 +3817,14 @@
       <c r="L42" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42" t="s">
+        <v>192</v>
+      </c>
+      <c r="N42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1</v>
       </c>
@@ -3573,22 +3832,22 @@
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>141.02930000000001</v>
-      </c>
-      <c r="G43" t="s">
-        <v>192</v>
-      </c>
-      <c r="H43" t="s">
-        <v>193</v>
+        <v>135.27052</v>
+      </c>
+      <c r="G43">
+        <v>0.9998274843991859</v>
+      </c>
+      <c r="H43">
+        <v>0.99987923907942999</v>
       </c>
       <c r="I43" t="s">
         <v>194</v>
@@ -3602,8 +3861,14 @@
       <c r="L43" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M43" t="s">
+        <v>198</v>
+      </c>
+      <c r="N43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1</v>
       </c>
@@ -3611,10 +3876,10 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3622,11 +3887,11 @@
       <c r="F44">
         <v>135.27052</v>
       </c>
-      <c r="G44" t="s">
-        <v>198</v>
-      </c>
-      <c r="H44" t="s">
-        <v>199</v>
+      <c r="G44">
+        <v>0.99975388973216262</v>
+      </c>
+      <c r="H44">
+        <v>0.99982772281251386</v>
       </c>
       <c r="I44" t="s">
         <v>200</v>
@@ -3640,8 +3905,14 @@
       <c r="L44" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M44" t="s">
+        <v>204</v>
+      </c>
+      <c r="N44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1</v>
       </c>
@@ -3649,22 +3920,22 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45">
-        <v>135.27052</v>
-      </c>
-      <c r="G45" t="s">
-        <v>204</v>
-      </c>
-      <c r="H45" t="s">
-        <v>205</v>
+        <v>142.86761000000001</v>
+      </c>
+      <c r="G45">
+        <v>0.99963375321517611</v>
+      </c>
+      <c r="H45">
+        <v>0.99974362725062327</v>
       </c>
       <c r="I45" t="s">
         <v>206</v>
@@ -3678,19 +3949,25 @@
       <c r="L45" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M45" t="s">
+        <v>210</v>
+      </c>
+      <c r="N45" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E46">
         <v>5</v>
@@ -3698,11 +3975,11 @@
       <c r="F46">
         <v>135.27052</v>
       </c>
-      <c r="G46" t="s">
-        <v>210</v>
-      </c>
-      <c r="H46" t="s">
-        <v>211</v>
+      <c r="G46">
+        <v>0.99945743525806741</v>
+      </c>
+      <c r="H46">
+        <v>0.99962020468064705</v>
       </c>
       <c r="I46" t="s">
         <v>212</v>
@@ -3716,8 +3993,14 @@
       <c r="L46" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M46" t="s">
+        <v>216</v>
+      </c>
+      <c r="N46" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3725,22 +4008,22 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E47">
         <v>6</v>
       </c>
       <c r="F47">
-        <v>135.27052</v>
-      </c>
-      <c r="G47" t="s">
-        <v>216</v>
-      </c>
-      <c r="H47" t="s">
-        <v>217</v>
+        <v>120.754555</v>
+      </c>
+      <c r="G47">
+        <v>0.99895203245071285</v>
+      </c>
+      <c r="H47">
+        <v>0.99926642271549904</v>
       </c>
       <c r="I47" t="s">
         <v>218</v>
@@ -3749,13 +4032,19 @@
         <v>219</v>
       </c>
       <c r="K47" t="s">
+        <v>202</v>
+      </c>
+      <c r="L47" t="s">
         <v>220</v>
       </c>
-      <c r="L47" t="s">
+      <c r="M47" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N47" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1</v>
       </c>
@@ -3763,37 +4052,43 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
       <c r="F48">
-        <v>127.60102999999999</v>
-      </c>
-      <c r="G48" t="s">
-        <v>222</v>
-      </c>
-      <c r="H48" t="s">
+        <v>135.27052</v>
+      </c>
+      <c r="G48">
+        <v>0.99868808582524582</v>
+      </c>
+      <c r="H48">
+        <v>0.99908166007767196</v>
+      </c>
+      <c r="I48" t="s">
         <v>223</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>224</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>225</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>226</v>
       </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N48" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1</v>
       </c>
@@ -3801,10 +4096,10 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E49">
         <v>8</v>
@@ -3812,26 +4107,32 @@
       <c r="F49">
         <v>127.60102999999999</v>
       </c>
-      <c r="G49" t="s">
-        <v>228</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="G49">
+        <v>0.99853306063089275</v>
+      </c>
+      <c r="H49">
+        <v>0.99897314244162483</v>
+      </c>
+      <c r="I49" t="s">
         <v>229</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>230</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>231</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>232</v>
       </c>
-      <c r="L49" t="s">
+      <c r="M49" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1</v>
       </c>
@@ -3839,10 +4140,10 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E50">
         <v>9</v>
@@ -3850,26 +4151,32 @@
       <c r="F50">
         <v>127.60102999999999</v>
       </c>
-      <c r="G50" t="s">
-        <v>234</v>
-      </c>
-      <c r="H50" t="s">
+      <c r="G50">
+        <v>0.9950275194292848</v>
+      </c>
+      <c r="H50">
+        <v>0.99651926360049936</v>
+      </c>
+      <c r="I50" t="s">
         <v>235</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>236</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>237</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>238</v>
       </c>
-      <c r="L50" t="s">
+      <c r="M50" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1</v>
       </c>
@@ -3877,25 +4184,25 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>120.754555</v>
-      </c>
-      <c r="G51" t="s">
-        <v>240</v>
-      </c>
-      <c r="H51" t="s">
+        <v>127.60102999999999</v>
+      </c>
+      <c r="G51">
+        <v>0.98276844085585491</v>
+      </c>
+      <c r="H51">
+        <v>0.98793790859909847</v>
+      </c>
+      <c r="I51" t="s">
         <v>241</v>
-      </c>
-      <c r="I51" t="s">
-        <v>206</v>
       </c>
       <c r="J51" t="s">
         <v>242</v>
@@ -3906,8 +4213,14 @@
       <c r="L51" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M51" t="s">
+        <v>245</v>
+      </c>
+      <c r="N51" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1</v>
       </c>
@@ -3915,10 +4228,10 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3926,11 +4239,11 @@
       <c r="F52">
         <v>68.005295000000004</v>
       </c>
-      <c r="G52" t="s">
-        <v>246</v>
-      </c>
-      <c r="H52" t="s">
-        <v>247</v>
+      <c r="G52">
+        <v>0.96870325635065113</v>
+      </c>
+      <c r="H52">
+        <v>0.88210816444545581</v>
       </c>
       <c r="I52" t="s">
         <v>248</v>
@@ -3944,8 +4257,14 @@
       <c r="L52" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M52" t="s">
+        <v>252</v>
+      </c>
+      <c r="N52" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1</v>
       </c>
@@ -3953,10 +4272,10 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E53">
         <v>2</v>
@@ -3964,11 +4283,11 @@
       <c r="F53">
         <v>62.176735000000001</v>
       </c>
-      <c r="G53" t="s">
-        <v>252</v>
-      </c>
-      <c r="H53" t="s">
-        <v>253</v>
+      <c r="G53">
+        <v>0.94877869295055484</v>
+      </c>
+      <c r="H53">
+        <v>0.85067529006538845</v>
       </c>
       <c r="I53" t="s">
         <v>254</v>
@@ -3982,8 +4301,14 @@
       <c r="L53" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M53" t="s">
+        <v>258</v>
+      </c>
+      <c r="N53" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1</v>
       </c>
@@ -3991,22 +4316,22 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
       <c r="F54">
-        <v>62.176735000000001</v>
-      </c>
-      <c r="G54" t="s">
-        <v>258</v>
-      </c>
-      <c r="H54" t="s">
-        <v>259</v>
+        <v>58.816090000000003</v>
+      </c>
+      <c r="G54">
+        <v>0.8934823727276745</v>
+      </c>
+      <c r="H54">
+        <v>0.8018859309093721</v>
       </c>
       <c r="I54" t="s">
         <v>260</v>
@@ -4020,8 +4345,14 @@
       <c r="L54" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M54" t="s">
+        <v>264</v>
+      </c>
+      <c r="N54" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1</v>
       </c>
@@ -4029,22 +4360,22 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E55">
         <v>4</v>
       </c>
       <c r="F55">
-        <v>58.816090000000003</v>
-      </c>
-      <c r="G55" t="s">
-        <v>264</v>
-      </c>
-      <c r="H55" t="s">
-        <v>265</v>
+        <v>41.359206999999998</v>
+      </c>
+      <c r="G55">
+        <v>0.68058274445529843</v>
+      </c>
+      <c r="H55">
+        <v>0.60048554211870886</v>
       </c>
       <c r="I55" t="s">
         <v>266</v>
@@ -4058,8 +4389,14 @@
       <c r="L55" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M55" t="s">
+        <v>270</v>
+      </c>
+      <c r="N55" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1</v>
       </c>
@@ -4067,22 +4404,22 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E56">
         <v>5</v>
       </c>
       <c r="F56">
-        <v>41.359206999999998</v>
-      </c>
-      <c r="G56" t="s">
-        <v>270</v>
-      </c>
-      <c r="H56" t="s">
-        <v>271</v>
+        <v>40.025157999999998</v>
+      </c>
+      <c r="G56">
+        <v>0.62181951804334756</v>
+      </c>
+      <c r="H56">
+        <v>0.55534913663034324</v>
       </c>
       <c r="I56" t="s">
         <v>272</v>
@@ -4096,46 +4433,58 @@
       <c r="L56" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M56" t="s">
+        <v>276</v>
+      </c>
+      <c r="N56" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E57">
         <v>6</v>
       </c>
       <c r="F57">
-        <v>40.025157999999998</v>
-      </c>
-      <c r="G57" t="s">
-        <v>276</v>
-      </c>
-      <c r="H57" t="s">
-        <v>277</v>
+        <v>38.774482999999996</v>
+      </c>
+      <c r="G57">
+        <v>0.45623608962630952</v>
+      </c>
+      <c r="H57">
+        <v>0.43568871173841661</v>
       </c>
       <c r="I57" t="s">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="J57" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K57" t="s">
-        <v>279</v>
+        <v>149</v>
       </c>
       <c r="L57" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M57" t="s">
+        <v>281</v>
+      </c>
+      <c r="N57" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1</v>
       </c>
@@ -4143,10 +4492,10 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E58">
         <v>7</v>
@@ -4154,11 +4503,11 @@
       <c r="F58">
         <v>40.025157999999998</v>
       </c>
-      <c r="G58" t="s">
-        <v>281</v>
-      </c>
-      <c r="H58" t="s">
-        <v>282</v>
+      <c r="G58">
+        <v>0.41814261943637621</v>
+      </c>
+      <c r="H58">
+        <v>0.41277530760546333</v>
       </c>
       <c r="I58" t="s">
         <v>283</v>
@@ -4172,31 +4521,37 @@
       <c r="L58" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M58" t="s">
+        <v>287</v>
+      </c>
+      <c r="N58" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E59">
         <v>8</v>
       </c>
       <c r="F59">
-        <v>40.025157999999998</v>
-      </c>
-      <c r="G59" t="s">
-        <v>287</v>
-      </c>
-      <c r="H59" t="s">
-        <v>288</v>
+        <v>62.176735000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.30586475495350829</v>
+      </c>
+      <c r="H59">
+        <v>0.40063553346745578</v>
       </c>
       <c r="I59" t="s">
         <v>289</v>
@@ -4210,8 +4565,14 @@
       <c r="L59" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M59" t="s">
+        <v>293</v>
+      </c>
+      <c r="N59" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1</v>
       </c>
@@ -4219,10 +4580,10 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E60">
         <v>9</v>
@@ -4230,11 +4591,11 @@
       <c r="F60">
         <v>40.025157999999998</v>
       </c>
-      <c r="G60" t="s">
-        <v>293</v>
-      </c>
-      <c r="H60" t="s">
-        <v>294</v>
+      <c r="G60">
+        <v>0.32614324237356368</v>
+      </c>
+      <c r="H60">
+        <v>0.3483757436614946</v>
       </c>
       <c r="I60" t="s">
         <v>295</v>
@@ -4248,8 +4609,14 @@
       <c r="L60" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M60" t="s">
+        <v>299</v>
+      </c>
+      <c r="N60" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1</v>
       </c>
@@ -4257,37 +4624,43 @@
         <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E61">
         <v>10</v>
       </c>
       <c r="F61">
-        <v>38.774482999999996</v>
-      </c>
-      <c r="G61" t="s">
-        <v>299</v>
-      </c>
-      <c r="H61" t="s">
-        <v>300</v>
+        <v>40.025157999999998</v>
+      </c>
+      <c r="G61">
+        <v>0.2352229847867402</v>
+      </c>
+      <c r="H61">
+        <v>0.28473156335071809</v>
       </c>
       <c r="I61" t="s">
-        <v>165</v>
+        <v>301</v>
       </c>
       <c r="J61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K61" t="s">
-        <v>302</v>
+        <v>45</v>
       </c>
       <c r="L61" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M61" t="s">
+        <v>304</v>
+      </c>
+      <c r="N61" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1</v>
       </c>
@@ -4295,10 +4668,10 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -4306,11 +4679,11 @@
       <c r="F62">
         <v>872.99270000000001</v>
       </c>
-      <c r="G62" t="s">
-        <v>305</v>
-      </c>
-      <c r="H62" t="s">
-        <v>306</v>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
       </c>
       <c r="I62" t="s">
         <v>307</v>
@@ -4324,8 +4697,14 @@
       <c r="L62" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M62" t="s">
+        <v>311</v>
+      </c>
+      <c r="N62" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1</v>
       </c>
@@ -4333,10 +4712,10 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -4344,11 +4723,11 @@
       <c r="F63">
         <v>726.61632999999995</v>
       </c>
-      <c r="G63" t="s">
-        <v>311</v>
-      </c>
-      <c r="H63" t="s">
-        <v>312</v>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
       </c>
       <c r="I63" t="s">
         <v>313</v>
@@ -4362,8 +4741,14 @@
       <c r="L63" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M63" t="s">
+        <v>317</v>
+      </c>
+      <c r="N63" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1</v>
       </c>
@@ -4371,10 +4756,10 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4382,11 +4767,11 @@
       <c r="F64">
         <v>692.81664999999998</v>
       </c>
-      <c r="G64" t="s">
-        <v>317</v>
-      </c>
-      <c r="H64" t="s">
-        <v>318</v>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
       </c>
       <c r="I64" t="s">
         <v>319</v>
@@ -4400,8 +4785,14 @@
       <c r="L64" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M64" t="s">
+        <v>323</v>
+      </c>
+      <c r="N64" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1</v>
       </c>
@@ -4409,10 +4800,10 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -4420,11 +4811,11 @@
       <c r="F65">
         <v>692.81664999999998</v>
       </c>
-      <c r="G65" t="s">
-        <v>323</v>
-      </c>
-      <c r="H65" t="s">
-        <v>324</v>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
       </c>
       <c r="I65" t="s">
         <v>325</v>
@@ -4438,8 +4829,14 @@
       <c r="L65" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M65" t="s">
+        <v>329</v>
+      </c>
+      <c r="N65" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1</v>
       </c>
@@ -4447,10 +4844,10 @@
         <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E66">
         <v>5</v>
@@ -4458,11 +4855,11 @@
       <c r="F66">
         <v>651.17470000000003</v>
       </c>
-      <c r="G66" t="s">
-        <v>329</v>
-      </c>
-      <c r="H66" t="s">
-        <v>330</v>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
       </c>
       <c r="I66" t="s">
         <v>331</v>
@@ -4476,8 +4873,14 @@
       <c r="L66" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M66" t="s">
+        <v>335</v>
+      </c>
+      <c r="N66" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1</v>
       </c>
@@ -4485,10 +4888,10 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D67" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E67">
         <v>6</v>
@@ -4496,11 +4899,11 @@
       <c r="F67">
         <v>651.17470000000003</v>
       </c>
-      <c r="G67" t="s">
-        <v>335</v>
-      </c>
-      <c r="H67" t="s">
-        <v>336</v>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
       </c>
       <c r="I67" t="s">
         <v>337</v>
@@ -4514,8 +4917,14 @@
       <c r="L67" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M67" t="s">
+        <v>341</v>
+      </c>
+      <c r="N67" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1</v>
       </c>
@@ -4523,10 +4932,10 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E68">
         <v>7</v>
@@ -4534,11 +4943,11 @@
       <c r="F68">
         <v>614.25476000000003</v>
       </c>
-      <c r="G68" t="s">
-        <v>341</v>
-      </c>
-      <c r="H68" t="s">
-        <v>342</v>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
       </c>
       <c r="I68" t="s">
         <v>343</v>
@@ -4552,8 +4961,14 @@
       <c r="L68" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M68" t="s">
+        <v>347</v>
+      </c>
+      <c r="N68" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1</v>
       </c>
@@ -4561,10 +4976,10 @@
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D69" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E69">
         <v>8</v>
@@ -4572,11 +4987,11 @@
       <c r="F69">
         <v>614.25476000000003</v>
       </c>
-      <c r="G69" t="s">
-        <v>347</v>
-      </c>
-      <c r="H69" t="s">
-        <v>348</v>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
       </c>
       <c r="I69" t="s">
         <v>349</v>
@@ -4590,8 +5005,14 @@
       <c r="L69" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M69" t="s">
+        <v>353</v>
+      </c>
+      <c r="N69" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1</v>
       </c>
@@ -4599,10 +5020,10 @@
         <v>7</v>
       </c>
       <c r="C70" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D70" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E70">
         <v>9</v>
@@ -4610,26 +5031,32 @@
       <c r="F70">
         <v>614.25476000000003</v>
       </c>
-      <c r="G70" t="s">
-        <v>353</v>
-      </c>
-      <c r="H70" t="s">
-        <v>354</v>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="J70" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K70" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="L70" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M70" t="s">
+        <v>358</v>
+      </c>
+      <c r="N70" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1</v>
       </c>
@@ -4637,10 +5064,10 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D71" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E71">
         <v>10</v>
@@ -4648,11 +5075,11 @@
       <c r="F71">
         <v>581.29669999999999</v>
       </c>
-      <c r="G71" t="s">
-        <v>358</v>
-      </c>
-      <c r="H71" t="s">
-        <v>359</v>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
       </c>
       <c r="I71" t="s">
         <v>360</v>
@@ -4666,8 +5093,14 @@
       <c r="L71" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M71" t="s">
+        <v>364</v>
+      </c>
+      <c r="N71" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1</v>
       </c>
@@ -4675,10 +5108,10 @@
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4686,11 +5119,11 @@
       <c r="F72">
         <v>43.861899999999999</v>
       </c>
-      <c r="G72" t="s">
-        <v>365</v>
-      </c>
-      <c r="H72" t="s">
-        <v>366</v>
+      <c r="G72">
+        <v>0.9023423428833719</v>
+      </c>
+      <c r="H72">
+        <v>0.76322534001836029</v>
       </c>
       <c r="I72" t="s">
         <v>367</v>
@@ -4704,31 +5137,37 @@
       <c r="L72" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M72" t="s">
+        <v>371</v>
+      </c>
+      <c r="N72" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73">
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E73">
         <v>2</v>
       </c>
       <c r="F73">
-        <v>43.861899999999999</v>
-      </c>
-      <c r="G73" t="s">
-        <v>371</v>
-      </c>
-      <c r="H73" t="s">
-        <v>372</v>
+        <v>34.967995000000002</v>
+      </c>
+      <c r="G73">
+        <v>0.7356600805885628</v>
+      </c>
+      <c r="H73">
+        <v>0.61986604141199386</v>
       </c>
       <c r="I73" t="s">
         <v>373</v>
@@ -4742,19 +5181,25 @@
       <c r="L73" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M73" t="s">
+        <v>377</v>
+      </c>
+      <c r="N73" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74">
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -4762,26 +5207,32 @@
       <c r="F74">
         <v>43.269024000000002</v>
       </c>
-      <c r="G74" t="s">
-        <v>377</v>
-      </c>
-      <c r="H74" t="s">
-        <v>378</v>
+      <c r="G74">
+        <v>0.69178761906754249</v>
+      </c>
+      <c r="H74">
+        <v>0.61405840534727973</v>
       </c>
       <c r="I74" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="J74" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K74" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="L74" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M74" t="s">
+        <v>382</v>
+      </c>
+      <c r="N74" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1</v>
       </c>
@@ -4789,22 +5240,22 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D75" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E75">
         <v>4</v>
       </c>
       <c r="F75">
-        <v>40.865349999999999</v>
-      </c>
-      <c r="G75" t="s">
-        <v>382</v>
-      </c>
-      <c r="H75" t="s">
-        <v>383</v>
+        <v>32.094769999999997</v>
+      </c>
+      <c r="G75">
+        <v>0.73774341114240427</v>
+      </c>
+      <c r="H75">
+        <v>0.61270469779968284</v>
       </c>
       <c r="I75" t="s">
         <v>384</v>
@@ -4818,8 +5269,14 @@
       <c r="L75" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M75" t="s">
+        <v>388</v>
+      </c>
+      <c r="N75" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1</v>
       </c>
@@ -4827,22 +5284,22 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D76" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>5</v>
       </c>
       <c r="F76">
-        <v>40.865349999999999</v>
-      </c>
-      <c r="G76" t="s">
-        <v>388</v>
-      </c>
-      <c r="H76" t="s">
-        <v>389</v>
+        <v>43.861899999999999</v>
+      </c>
+      <c r="G76">
+        <v>0.65064536693288499</v>
+      </c>
+      <c r="H76">
+        <v>0.58703745685301945</v>
       </c>
       <c r="I76" t="s">
         <v>390</v>
@@ -4856,8 +5313,14 @@
       <c r="L76" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M76" t="s">
+        <v>394</v>
+      </c>
+      <c r="N76" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>0</v>
       </c>
@@ -4865,22 +5328,22 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E77">
         <v>6</v>
       </c>
       <c r="F77">
-        <v>40.096220000000002</v>
-      </c>
-      <c r="G77" t="s">
-        <v>394</v>
-      </c>
-      <c r="H77" t="s">
-        <v>395</v>
+        <v>31.002800000000001</v>
+      </c>
+      <c r="G77">
+        <v>0.67338543755049829</v>
+      </c>
+      <c r="H77">
+        <v>0.56437820628534874</v>
       </c>
       <c r="I77" t="s">
         <v>396</v>
@@ -4889,89 +5352,107 @@
         <v>397</v>
       </c>
       <c r="K77" t="s">
+        <v>369</v>
+      </c>
+      <c r="L77" t="s">
         <v>398</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N77" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78">
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E78">
         <v>7</v>
       </c>
       <c r="F78">
-        <v>34.967995000000002</v>
-      </c>
-      <c r="G78" t="s">
-        <v>400</v>
-      </c>
-      <c r="H78" t="s">
+        <v>33.914462999999998</v>
+      </c>
+      <c r="G78">
+        <v>0.59136170442900549</v>
+      </c>
+      <c r="H78">
+        <v>0.51569658210030378</v>
+      </c>
+      <c r="I78" t="s">
         <v>401</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>402</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
+        <v>369</v>
+      </c>
+      <c r="L78" t="s">
         <v>403</v>
       </c>
-      <c r="K78" t="s">
+      <c r="M78" t="s">
+        <v>371</v>
+      </c>
+      <c r="N78" t="s">
         <v>404</v>
       </c>
-      <c r="L78" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B79">
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D79" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E79">
         <v>8</v>
       </c>
       <c r="F79">
-        <v>33.914462999999998</v>
-      </c>
-      <c r="G79" t="s">
+        <v>40.096220000000002</v>
+      </c>
+      <c r="G79">
+        <v>0.54457777947460073</v>
+      </c>
+      <c r="H79">
+        <v>0.50149310563222049</v>
+      </c>
+      <c r="I79" t="s">
+        <v>405</v>
+      </c>
+      <c r="J79" t="s">
         <v>406</v>
       </c>
-      <c r="H79" t="s">
+      <c r="K79" t="s">
         <v>407</v>
       </c>
-      <c r="I79" t="s">
-        <v>367</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="L79" t="s">
         <v>408</v>
       </c>
-      <c r="K79" t="s">
-        <v>369</v>
-      </c>
-      <c r="L79" t="s">
+      <c r="M79" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N79" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1</v>
       </c>
@@ -4979,63 +5460,69 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D80" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E80">
         <v>9</v>
       </c>
       <c r="F80">
-        <v>32.094769999999997</v>
-      </c>
-      <c r="G80" t="s">
-        <v>410</v>
-      </c>
-      <c r="H80" t="s">
+        <v>40.865349999999999</v>
+      </c>
+      <c r="G80">
+        <v>0.48865942216099051</v>
+      </c>
+      <c r="H80">
+        <v>0.46465764551269328</v>
+      </c>
+      <c r="I80" t="s">
         <v>411</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>412</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>413</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>414</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N80" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81">
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E81">
         <v>10</v>
       </c>
       <c r="F81">
-        <v>31.002800000000001</v>
-      </c>
-      <c r="G81" t="s">
-        <v>416</v>
-      </c>
-      <c r="H81" t="s">
+        <v>40.865349999999999</v>
+      </c>
+      <c r="G81">
+        <v>0.36938520169972161</v>
+      </c>
+      <c r="H81">
+        <v>0.38116569118980509</v>
+      </c>
+      <c r="I81" t="s">
         <v>417</v>
-      </c>
-      <c r="I81" t="s">
-        <v>367</v>
       </c>
       <c r="J81" t="s">
         <v>418</v>
@@ -5046,8 +5533,14 @@
       <c r="L81" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M81" t="s">
+        <v>421</v>
+      </c>
+      <c r="N81" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1</v>
       </c>
@@ -5055,22 +5548,22 @@
         <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D82" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>62.738937</v>
-      </c>
-      <c r="G82" t="s">
-        <v>422</v>
-      </c>
-      <c r="H82" t="s">
-        <v>423</v>
+        <v>57.712085999999999</v>
+      </c>
+      <c r="G82">
+        <v>0.96399922388705028</v>
+      </c>
+      <c r="H82">
+        <v>0.8479357147209351</v>
       </c>
       <c r="I82" t="s">
         <v>424</v>
@@ -5084,8 +5577,14 @@
       <c r="L82" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M82" t="s">
+        <v>428</v>
+      </c>
+      <c r="N82" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1</v>
       </c>
@@ -5093,37 +5592,43 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E83">
         <v>2</v>
       </c>
       <c r="F83">
-        <v>60.094658000000003</v>
-      </c>
-      <c r="G83" t="s">
-        <v>428</v>
-      </c>
-      <c r="H83" t="s">
-        <v>429</v>
+        <v>55.54927</v>
+      </c>
+      <c r="G83">
+        <v>0.96482786767828699</v>
+      </c>
+      <c r="H83">
+        <v>0.84202731737480085</v>
       </c>
       <c r="I83" t="s">
-        <v>74</v>
+        <v>430</v>
       </c>
       <c r="J83" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K83" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L83" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="M83" t="s">
+        <v>434</v>
+      </c>
+      <c r="N83" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1</v>
       </c>
@@ -5131,37 +5636,43 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84">
-        <v>59.617843999999998</v>
-      </c>
-      <c r="G84" t="s">
-        <v>433</v>
-      </c>
-      <c r="H84" t="s">
-        <v>434</v>
+        <v>57.712085999999999</v>
+      </c>
+      <c r="G84">
+        <v>0.95390763964719349</v>
+      </c>
+      <c r="H84">
+        <v>0.84087160575303543</v>
       </c>
       <c r="I84" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J84" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K84" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L84" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+      <c r="M84" t="s">
+        <v>440</v>
+      </c>
+      <c r="N84" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1</v>
       </c>
@@ -5169,37 +5680,43 @@
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E85">
         <v>4</v>
       </c>
       <c r="F85">
-        <v>57.712085999999999</v>
-      </c>
-      <c r="G85" t="s">
-        <v>439</v>
-      </c>
-      <c r="H85" t="s">
-        <v>440</v>
+        <v>53.573300000000003</v>
+      </c>
+      <c r="G85">
+        <v>0.93011695708171971</v>
+      </c>
+      <c r="H85">
+        <v>0.81180176995720377</v>
       </c>
       <c r="I85" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J85" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K85" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L85" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+      <c r="M85" t="s">
+        <v>446</v>
+      </c>
+      <c r="N85" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1</v>
       </c>
@@ -5207,37 +5724,43 @@
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E86">
         <v>5</v>
       </c>
       <c r="F86">
-        <v>57.712085999999999</v>
-      </c>
-      <c r="G86" t="s">
-        <v>445</v>
-      </c>
-      <c r="H86" t="s">
-        <v>446</v>
+        <v>53.573300000000003</v>
+      </c>
+      <c r="G86">
+        <v>0.90789811428164147</v>
+      </c>
+      <c r="H86">
+        <v>0.79624857999714904</v>
       </c>
       <c r="I86" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J86" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K86" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="L86" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M86" t="s">
+        <v>451</v>
+      </c>
+      <c r="N86" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1</v>
       </c>
@@ -5245,22 +5768,22 @@
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E87">
         <v>6</v>
       </c>
       <c r="F87">
-        <v>55.54927</v>
-      </c>
-      <c r="G87" t="s">
-        <v>451</v>
-      </c>
-      <c r="H87" t="s">
-        <v>452</v>
+        <v>62.738937</v>
+      </c>
+      <c r="G87">
+        <v>0.85028720645602607</v>
+      </c>
+      <c r="H87">
+        <v>0.78341785551921816</v>
       </c>
       <c r="I87" t="s">
         <v>453</v>
@@ -5274,8 +5797,14 @@
       <c r="L87" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M87" t="s">
+        <v>457</v>
+      </c>
+      <c r="N87" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1</v>
       </c>
@@ -5283,37 +5812,43 @@
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E88">
         <v>7</v>
       </c>
       <c r="F88">
-        <v>53.710410000000003</v>
-      </c>
-      <c r="G88" t="s">
-        <v>457</v>
-      </c>
-      <c r="H88" t="s">
-        <v>458</v>
+        <v>53.573300000000003</v>
+      </c>
+      <c r="G88">
+        <v>0.88872857661097626</v>
+      </c>
+      <c r="H88">
+        <v>0.78282990362768334</v>
       </c>
       <c r="I88" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="J88" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K88" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L88" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+      <c r="M88" t="s">
+        <v>463</v>
+      </c>
+      <c r="N88" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1</v>
       </c>
@@ -5321,37 +5856,43 @@
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E89">
         <v>8</v>
       </c>
       <c r="F89">
-        <v>53.573300000000003</v>
-      </c>
-      <c r="G89" t="s">
-        <v>462</v>
-      </c>
-      <c r="H89" t="s">
-        <v>463</v>
+        <v>59.617843999999998</v>
+      </c>
+      <c r="G89">
+        <v>0.83500224252340327</v>
+      </c>
+      <c r="H89">
+        <v>0.76335510176638222</v>
       </c>
       <c r="I89" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J89" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K89" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L89" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+      <c r="M89" t="s">
+        <v>469</v>
+      </c>
+      <c r="N89" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1</v>
       </c>
@@ -5359,37 +5900,43 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E90">
         <v>9</v>
       </c>
       <c r="F90">
-        <v>53.573300000000003</v>
-      </c>
-      <c r="G90" t="s">
-        <v>468</v>
-      </c>
-      <c r="H90" t="s">
-        <v>469</v>
+        <v>60.094658000000003</v>
+      </c>
+      <c r="G90">
+        <v>0.81144566236447702</v>
+      </c>
+      <c r="H90">
+        <v>0.7482959376551338</v>
       </c>
       <c r="I90" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J90" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K90" t="s">
-        <v>472</v>
+        <v>91</v>
       </c>
       <c r="L90" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M90" t="s">
+        <v>474</v>
+      </c>
+      <c r="N90" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1</v>
       </c>
@@ -5397,37 +5944,43 @@
         <v>9</v>
       </c>
       <c r="C91" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E91">
         <v>10</v>
       </c>
       <c r="F91">
-        <v>53.573300000000003</v>
-      </c>
-      <c r="G91" t="s">
-        <v>474</v>
-      </c>
-      <c r="H91" t="s">
-        <v>475</v>
+        <v>53.710410000000003</v>
+      </c>
+      <c r="G91">
+        <v>0.82630668783023142</v>
+      </c>
+      <c r="H91">
+        <v>0.739545911481162</v>
       </c>
       <c r="I91" t="s">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="J91" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K91" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="L91" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M91" t="s">
+        <v>479</v>
+      </c>
+      <c r="N91" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1</v>
       </c>
@@ -5435,10 +5988,10 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -5446,11 +5999,11 @@
       <c r="F92">
         <v>57.344634999999997</v>
       </c>
-      <c r="G92" t="s">
-        <v>480</v>
-      </c>
-      <c r="H92" t="s">
-        <v>481</v>
+      <c r="G92">
+        <v>0.85863335267421659</v>
+      </c>
+      <c r="H92">
+        <v>0.77307725187195153</v>
       </c>
       <c r="I92" t="s">
         <v>482</v>
@@ -5464,8 +6017,14 @@
       <c r="L92" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M92" t="s">
+        <v>486</v>
+      </c>
+      <c r="N92" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1</v>
       </c>
@@ -5473,113 +6032,131 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D93" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93">
-        <v>51.607460000000003</v>
-      </c>
-      <c r="G93" t="s">
-        <v>486</v>
-      </c>
-      <c r="H93" t="s">
-        <v>487</v>
+        <v>42.236282000000003</v>
+      </c>
+      <c r="G93">
+        <v>0.66520337183408917</v>
+      </c>
+      <c r="H93">
+        <v>0.5923512062838624</v>
       </c>
       <c r="I93" t="s">
-        <v>488</v>
+        <v>260</v>
       </c>
       <c r="J93" t="s">
-        <v>489</v>
+        <v>261</v>
       </c>
       <c r="K93" t="s">
-        <v>490</v>
+        <v>262</v>
       </c>
       <c r="L93" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="M93" t="s">
+        <v>264</v>
+      </c>
+      <c r="N93" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94">
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D94" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94">
-        <v>45.500279999999997</v>
-      </c>
-      <c r="G94" t="s">
+        <v>51.607460000000003</v>
+      </c>
+      <c r="G94">
+        <v>0.56782864369355734</v>
+      </c>
+      <c r="H94">
+        <v>0.55230243058549011</v>
+      </c>
+      <c r="I94" t="s">
+        <v>488</v>
+      </c>
+      <c r="J94" t="s">
+        <v>489</v>
+      </c>
+      <c r="K94" t="s">
+        <v>490</v>
+      </c>
+      <c r="L94" t="s">
+        <v>491</v>
+      </c>
+      <c r="M94" t="s">
         <v>492</v>
       </c>
-      <c r="H94" t="s">
+      <c r="N94" t="s">
         <v>493</v>
       </c>
-      <c r="I94" t="s">
-        <v>494</v>
-      </c>
-      <c r="J94" t="s">
-        <v>495</v>
-      </c>
-      <c r="K94" t="s">
-        <v>496</v>
-      </c>
-      <c r="L94" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B95">
         <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="F95">
-        <v>43.801895000000002</v>
-      </c>
-      <c r="G95" t="s">
+        <v>39.824745</v>
+      </c>
+      <c r="G95">
+        <v>0.58381539381918091</v>
+      </c>
+      <c r="H95">
+        <v>0.52814501067342667</v>
+      </c>
+      <c r="I95" t="s">
+        <v>494</v>
+      </c>
+      <c r="J95" t="s">
+        <v>495</v>
+      </c>
+      <c r="K95" t="s">
+        <v>496</v>
+      </c>
+      <c r="L95" t="s">
+        <v>497</v>
+      </c>
+      <c r="M95" t="s">
         <v>498</v>
       </c>
-      <c r="H95" t="s">
+      <c r="N95" t="s">
         <v>499</v>
       </c>
-      <c r="I95" t="s">
-        <v>500</v>
-      </c>
-      <c r="J95" t="s">
-        <v>501</v>
-      </c>
-      <c r="K95" t="s">
-        <v>502</v>
-      </c>
-      <c r="L95" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1</v>
       </c>
@@ -5587,37 +6164,43 @@
         <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E96">
         <v>5</v>
       </c>
       <c r="F96">
-        <v>42.236282000000003</v>
-      </c>
-      <c r="G96" t="s">
-        <v>264</v>
-      </c>
-      <c r="H96" t="s">
-        <v>265</v>
+        <v>39.824745</v>
+      </c>
+      <c r="G96">
+        <v>0.5610149504724008</v>
+      </c>
+      <c r="H96">
+        <v>0.51218470033068053</v>
       </c>
       <c r="I96" t="s">
-        <v>266</v>
+        <v>500</v>
       </c>
       <c r="J96" t="s">
-        <v>267</v>
+        <v>501</v>
       </c>
       <c r="K96" t="s">
-        <v>268</v>
+        <v>496</v>
       </c>
       <c r="L96" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+      <c r="M96" t="s">
+        <v>498</v>
+      </c>
+      <c r="N96" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>0</v>
       </c>
@@ -5625,10 +6208,10 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D97" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E97">
         <v>6</v>
@@ -5636,26 +6219,32 @@
       <c r="F97">
         <v>39.824745</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G97">
+        <v>0.55248328323657259</v>
+      </c>
+      <c r="H97">
+        <v>0.50621253326560078</v>
+      </c>
+      <c r="I97" t="s">
         <v>504</v>
       </c>
-      <c r="H97" t="s">
+      <c r="J97" t="s">
         <v>505</v>
       </c>
-      <c r="I97" t="s">
+      <c r="K97" t="s">
+        <v>496</v>
+      </c>
+      <c r="L97" t="s">
         <v>506</v>
       </c>
-      <c r="J97" t="s">
+      <c r="M97" t="s">
+        <v>498</v>
+      </c>
+      <c r="N97" t="s">
         <v>507</v>
       </c>
-      <c r="K97" t="s">
-        <v>508</v>
-      </c>
-      <c r="L97" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1</v>
       </c>
@@ -5663,37 +6252,43 @@
         <v>10</v>
       </c>
       <c r="C98" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D98" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E98">
         <v>7</v>
       </c>
       <c r="F98">
-        <v>39.824745</v>
-      </c>
-      <c r="G98" t="s">
+        <v>38.710814999999997</v>
+      </c>
+      <c r="G98">
+        <v>0.50418567365929212</v>
+      </c>
+      <c r="H98">
+        <v>0.46906241656150438</v>
+      </c>
+      <c r="I98" t="s">
+        <v>508</v>
+      </c>
+      <c r="J98" t="s">
+        <v>509</v>
+      </c>
+      <c r="K98" t="s">
+        <v>467</v>
+      </c>
+      <c r="L98" t="s">
         <v>510</v>
       </c>
-      <c r="H98" t="s">
+      <c r="M98" t="s">
         <v>511</v>
       </c>
-      <c r="I98" t="s">
-        <v>506</v>
-      </c>
-      <c r="J98" t="s">
+      <c r="N98" t="s">
         <v>512</v>
       </c>
-      <c r="K98" t="s">
-        <v>508</v>
-      </c>
-      <c r="L98" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1</v>
       </c>
@@ -5701,110 +6296,128 @@
         <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D99" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E99">
         <v>8</v>
       </c>
       <c r="F99">
-        <v>39.824745</v>
-      </c>
-      <c r="G99" t="s">
+        <v>45.500279999999997</v>
+      </c>
+      <c r="G99">
+        <v>0.46581370432634972</v>
+      </c>
+      <c r="H99">
+        <v>0.46257043302844469</v>
+      </c>
+      <c r="I99" t="s">
+        <v>513</v>
+      </c>
+      <c r="J99" t="s">
         <v>514</v>
       </c>
-      <c r="H99" t="s">
+      <c r="K99" t="s">
         <v>515</v>
       </c>
-      <c r="I99" t="s">
-        <v>506</v>
-      </c>
-      <c r="J99" t="s">
+      <c r="L99" t="s">
         <v>516</v>
       </c>
-      <c r="K99" t="s">
-        <v>508</v>
-      </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N99" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B100">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D100" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E100">
         <v>9</v>
       </c>
       <c r="F100">
-        <v>39.824745</v>
-      </c>
-      <c r="G100" t="s">
-        <v>518</v>
-      </c>
-      <c r="H100" t="s">
+        <v>43.801895000000002</v>
+      </c>
+      <c r="G100">
+        <v>0.4413780732989403</v>
+      </c>
+      <c r="H100">
+        <v>0.4403703363092582</v>
+      </c>
+      <c r="I100" t="s">
         <v>519</v>
-      </c>
-      <c r="I100" t="s">
-        <v>506</v>
       </c>
       <c r="J100" t="s">
         <v>520</v>
       </c>
       <c r="K100" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="L100" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+      <c r="M100" t="s">
+        <v>523</v>
+      </c>
+      <c r="N100" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101">
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D101" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E101">
         <v>10</v>
       </c>
       <c r="F101">
-        <v>38.710814999999997</v>
-      </c>
-      <c r="G101" t="s">
-        <v>522</v>
-      </c>
-      <c r="H101" t="s">
-        <v>523</v>
+        <v>39.824745</v>
+      </c>
+      <c r="G101">
+        <v>0.40248447321981978</v>
+      </c>
+      <c r="H101">
+        <v>0.40121336625387383</v>
       </c>
       <c r="I101" t="s">
-        <v>435</v>
+        <v>525</v>
       </c>
       <c r="J101" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K101" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="L101" t="s">
-        <v>526</v>
+        <v>527</v>
+      </c>
+      <c r="M101" t="s">
+        <v>498</v>
+      </c>
+      <c r="N101" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>
